--- a/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
+++ b/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/Documents/GitHub/BUS210---Final-Exam-Practice-Problems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55DD8EB9-3971-4515-8668-473B9E338CA3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8A322C-9C37-40D2-825F-6AE31DEE0053}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TVM #1-15" sheetId="19" r:id="rId1"/>
@@ -21,19 +21,18 @@
     <sheet name="TVM #6-11" sheetId="35" r:id="rId6"/>
     <sheet name="Bond #1-20" sheetId="21" r:id="rId7"/>
     <sheet name="Bond #2-19" sheetId="22" r:id="rId8"/>
-    <sheet name="Bond #3 -2" sheetId="23" r:id="rId9"/>
-    <sheet name="Bond #4-18" sheetId="24" r:id="rId10"/>
-    <sheet name="Bond #5-16" sheetId="16" r:id="rId11"/>
-    <sheet name="Bond #6-14" sheetId="33" r:id="rId12"/>
-    <sheet name="Equity #1-1" sheetId="25" r:id="rId13"/>
-    <sheet name="Equity #2-3" sheetId="26" r:id="rId14"/>
-    <sheet name="Equity #3-4" sheetId="27" r:id="rId15"/>
-    <sheet name="Equity #4-5" sheetId="15" r:id="rId16"/>
-    <sheet name="Equity #5-12" sheetId="30" r:id="rId17"/>
-    <sheet name="Equity #6-13" sheetId="31" r:id="rId18"/>
-    <sheet name="WACC #1-6" sheetId="17" r:id="rId19"/>
-    <sheet name="WACC #2-7" sheetId="28" r:id="rId20"/>
-    <sheet name="WACC #3-17" sheetId="2" r:id="rId21"/>
+    <sheet name="Bond #4-18" sheetId="24" r:id="rId9"/>
+    <sheet name="Bond #5-16" sheetId="16" r:id="rId10"/>
+    <sheet name="Bond #6-14" sheetId="33" r:id="rId11"/>
+    <sheet name="Equity #1-1" sheetId="25" r:id="rId12"/>
+    <sheet name="Equity #2-3" sheetId="26" r:id="rId13"/>
+    <sheet name="Equity #3-4" sheetId="27" r:id="rId14"/>
+    <sheet name="Equity #4-5" sheetId="15" r:id="rId15"/>
+    <sheet name="Equity #5-12" sheetId="30" r:id="rId16"/>
+    <sheet name="Equity #6-13" sheetId="31" r:id="rId17"/>
+    <sheet name="WACC #1-6" sheetId="17" r:id="rId18"/>
+    <sheet name="WACC #2-7" sheetId="28" r:id="rId19"/>
+    <sheet name="WACC #3-17" sheetId="2" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="322">
   <si>
     <t>Beta</t>
   </si>
@@ -697,27 +696,6 @@
   </si>
   <si>
     <t>What is the total return % earned?</t>
-  </si>
-  <si>
-    <t>D=-∆P/(P_0*∆Y)</t>
-  </si>
-  <si>
-    <t>Dollar Value Version</t>
-  </si>
-  <si>
-    <t>Bond Price Version</t>
-  </si>
-  <si>
-    <t>Starting Price</t>
-  </si>
-  <si>
-    <t>Ending Price</t>
-  </si>
-  <si>
-    <t>Starting Yield</t>
-  </si>
-  <si>
-    <t>Ending Yield</t>
   </si>
   <si>
     <t xml:space="preserve"> Yields of a Bond</t>
@@ -1808,7 +1786,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2091,21 +2069,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2699,10 +2662,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="285" t="s">
+      <c r="B8" s="280" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="286"/>
+      <c r="C8" s="281"/>
     </row>
     <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="71" t="s">
@@ -2784,7 +2747,7 @@
         <v>98</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,274 +2812,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93BCCDF-AEB1-4B38-A1E0-2C0745BFEA03}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="289" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-    </row>
-    <row r="2" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="288" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="288"/>
-      <c r="C2" s="288"/>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="288"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="288" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="288"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="288" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="288"/>
-      <c r="C4" s="288"/>
-      <c r="D4" s="288"/>
-      <c r="E4" s="288"/>
-      <c r="F4" s="288"/>
-      <c r="G4" s="288"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="288" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="288"/>
-      <c r="C5" s="288"/>
-      <c r="D5" s="288"/>
-      <c r="E5" s="288"/>
-      <c r="F5" s="288"/>
-      <c r="G5" s="288"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="288" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="288"/>
-      <c r="C6" s="288"/>
-      <c r="D6" s="288"/>
-      <c r="E6" s="288"/>
-      <c r="F6" s="288"/>
-      <c r="G6" s="288"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="166"/>
-      <c r="B7" s="166"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
-      <c r="G7" s="166"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="167">
-        <v>0.98450000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="168" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="169">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="170" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="171">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="170" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="172">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="173" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="174">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="170" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="175">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="176" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="177">
-        <f>B13*B10</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="5">
-        <f>B11*2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="5">
-        <f>B12*2</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="178">
-        <f>B14/2</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="12">
-        <f>B8*B10</f>
-        <v>984.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="12">
-        <f>B14</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="12">
-        <f>B21+B10</f>
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
-        <v>218</v>
-      </c>
-      <c r="B24" s="179">
-        <f>B14/B20</f>
-        <v>4.5708481462671403E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" s="180">
-        <f>RATE(B16,-B18,B20,-B10)</f>
-        <v>2.3223120114168081E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="66">
-        <f>B26*2</f>
-        <v>4.6446240228336162E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="180">
-        <f>RATE(B17,-B18,B20,-B22)</f>
-        <v>2.8257927444819992E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="66">
-        <f>B29*2</f>
-        <v>5.6515854889639984E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="86" t="s">
-        <v>222</v>
-      </c>
-      <c r="B32" s="181">
-        <f>B27/(1-B9)</f>
-        <v>7.2572250356775253E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D61A856-DAAF-457A-805A-BE6676D4C18E}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -3266,7 +2961,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="I11" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J11" s="130">
         <v>0.05</v>
@@ -3431,7 +3126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274186D6-0845-4086-8645-5129374C9F00}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -3451,12 +3146,12 @@
     </row>
     <row r="2" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3470,62 +3165,62 @@
     <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="126"/>
       <c r="D11" s="126" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E11" s="126" t="s">
-        <v>317</v>
-      </c>
-      <c r="F11" s="247" t="s">
-        <v>222</v>
+        <v>310</v>
+      </c>
+      <c r="F11" s="242" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="245">
+        <v>292</v>
+      </c>
+      <c r="C12" s="240">
         <v>0.04</v>
       </c>
       <c r="D12" s="64"/>
-      <c r="E12" s="245">
+      <c r="E12" s="240">
         <f>C12+D12</f>
         <v>0.04</v>
       </c>
-      <c r="F12" s="245">
+      <c r="F12" s="240">
         <f>E12</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13" s="245"/>
-      <c r="D13" s="245">
+        <v>293</v>
+      </c>
+      <c r="C13" s="240"/>
+      <c r="D13" s="240">
         <v>0.02</v>
       </c>
-      <c r="E13" s="245">
+      <c r="E13" s="240">
         <f>C12+D13</f>
         <v>0.06</v>
       </c>
-      <c r="F13" s="245">
+      <c r="F13" s="240">
         <f>E13</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="245"/>
-      <c r="D14" s="245">
+        <v>294</v>
+      </c>
+      <c r="C14" s="240"/>
+      <c r="D14" s="240">
         <v>0.01</v>
       </c>
-      <c r="E14" s="245">
+      <c r="E14" s="240">
         <f>C12+D14</f>
         <v>0.05</v>
       </c>
-      <c r="F14" s="246">
+      <c r="F14" s="241">
         <f>E14/(1-B9)</f>
         <v>7.8125E-2</v>
       </c>
@@ -3540,7 +3235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A65F9133-00E1-449E-9ADA-4CB5979256BB}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -3955,7 +3650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6771D98C-B68B-4928-87E0-6C7B1111504C}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -3984,104 +3679,104 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D1" s="64"/>
       <c r="G1" s="64"/>
       <c r="H1" s="64"/>
       <c r="N1"/>
-      <c r="O1" s="182" t="s">
-        <v>224</v>
-      </c>
-      <c r="P1" s="183">
+      <c r="O1" s="177" t="s">
+        <v>217</v>
+      </c>
+      <c r="P1" s="178">
         <v>30000</v>
       </c>
       <c r="Q1"/>
       <c r="R1"/>
     </row>
     <row r="2" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="179" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="181" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" s="182" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="183" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="183" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" s="184" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2" s="184" t="s">
+        <v>224</v>
+      </c>
+      <c r="I2" s="184" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="185" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="186" t="s">
+      <c r="J2" s="184" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="K2" s="184" t="s">
         <v>227</v>
       </c>
-      <c r="E2" s="188" t="s">
+      <c r="L2" s="184" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="188" t="s">
+      <c r="M2" s="184" t="s">
         <v>229</v>
       </c>
-      <c r="G2" s="189" t="s">
+      <c r="N2"/>
+      <c r="O2" s="185" t="s">
         <v>230</v>
       </c>
-      <c r="H2" s="189" t="s">
-        <v>231</v>
-      </c>
-      <c r="I2" s="189" t="s">
-        <v>232</v>
-      </c>
-      <c r="J2" s="189" t="s">
-        <v>233</v>
-      </c>
-      <c r="K2" s="189" t="s">
-        <v>234</v>
-      </c>
-      <c r="L2" s="189" t="s">
-        <v>235</v>
-      </c>
-      <c r="M2" s="189" t="s">
-        <v>236</v>
-      </c>
-      <c r="N2"/>
-      <c r="O2" s="190" t="s">
-        <v>237</v>
-      </c>
-      <c r="P2" s="191">
+      <c r="P2" s="186">
         <v>1.6</v>
       </c>
       <c r="Q2"/>
       <c r="R2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="192" t="s">
-        <v>238</v>
-      </c>
-      <c r="B3" s="193">
+      <c r="A3" s="187" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="188">
         <f>P3</f>
         <v>2</v>
       </c>
-      <c r="C3" s="242">
+      <c r="C3" s="237">
         <v>16</v>
       </c>
-      <c r="D3" s="194">
+      <c r="D3" s="189">
         <f>ROUNDDOWN(E3/C3,0)</f>
         <v>875</v>
       </c>
-      <c r="E3" s="195">
+      <c r="E3" s="190">
         <f>F3*E5</f>
         <v>14000.000000000004</v>
       </c>
-      <c r="F3" s="250">
+      <c r="F3" s="245">
         <f>P5</f>
         <v>0.46666666666666679</v>
       </c>
-      <c r="G3" s="196">
+      <c r="G3" s="191">
         <f>(E3/$E$5)*B3</f>
         <v>0.93333333333333357</v>
       </c>
-      <c r="H3" s="197">
+      <c r="H3" s="192">
         <f>$B$8+B3*($B$7-$B$8)</f>
         <v>0.21</v>
       </c>
-      <c r="I3" s="198"/>
-      <c r="J3" s="199">
+      <c r="I3" s="193"/>
+      <c r="J3" s="194">
         <f>C3*(1+H3)-I3</f>
         <v>19.36</v>
       </c>
@@ -4097,90 +3792,90 @@
         <v>1.1239669421487601</v>
       </c>
       <c r="N3"/>
-      <c r="O3" s="182" t="s">
-        <v>239</v>
-      </c>
-      <c r="P3" s="200">
+      <c r="O3" s="177" t="s">
+        <v>232</v>
+      </c>
+      <c r="P3" s="195">
         <v>2</v>
       </c>
       <c r="Q3"/>
       <c r="R3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="201" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="202">
+      <c r="A4" s="196" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="197">
         <f>P4</f>
         <v>1.25</v>
       </c>
-      <c r="C4" s="243">
+      <c r="C4" s="238">
         <v>25</v>
       </c>
-      <c r="D4" s="194">
+      <c r="D4" s="189">
         <f>ROUNDDOWN(E4/C4,0)</f>
         <v>640</v>
       </c>
-      <c r="E4" s="203">
+      <c r="E4" s="198">
         <f>F4*E5</f>
         <v>15999.999999999996</v>
       </c>
-      <c r="F4" s="251">
+      <c r="F4" s="246">
         <f>P6</f>
         <v>0.53333333333333321</v>
       </c>
-      <c r="G4" s="204">
+      <c r="G4" s="199">
         <f>(E4/$E$5)*B4</f>
         <v>0.66666666666666652</v>
       </c>
-      <c r="H4" s="205">
+      <c r="H4" s="200">
         <f>$B$8+B4*($B$7-$B$8)</f>
         <v>0.14249999999999999</v>
       </c>
-      <c r="I4" s="241">
+      <c r="I4" s="236">
         <v>1</v>
       </c>
-      <c r="J4" s="206">
+      <c r="J4" s="201">
         <f>C4*(1+H4)-I4</f>
         <v>27.5625</v>
       </c>
       <c r="N4"/>
-      <c r="O4" s="190" t="s">
-        <v>241</v>
-      </c>
-      <c r="P4" s="207">
+      <c r="O4" s="185" t="s">
+        <v>234</v>
+      </c>
+      <c r="P4" s="202">
         <v>1.25</v>
       </c>
       <c r="Q4"/>
       <c r="R4"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="208" t="s">
-        <v>242</v>
-      </c>
-      <c r="B5" s="198"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="209">
+      <c r="A5" s="203" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="191"/>
+      <c r="E5" s="204">
         <f>P1</f>
         <v>30000</v>
       </c>
-      <c r="F5" s="210"/>
-      <c r="G5" s="211">
+      <c r="F5" s="205"/>
+      <c r="G5" s="206">
         <f>SUM(G3:G4)</f>
         <v>1.6</v>
       </c>
-      <c r="H5" s="212">
+      <c r="H5" s="207">
         <f>SUMPRODUCT(F3:F4,H3:H4)</f>
         <v>0.17399999999999999</v>
       </c>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="193"/>
       <c r="N5"/>
-      <c r="O5" s="213" t="s">
-        <v>243</v>
-      </c>
-      <c r="P5" s="248">
+      <c r="O5" s="208" t="s">
+        <v>236</v>
+      </c>
+      <c r="P5" s="243">
         <f>(P2-P4)/(P3-P4)</f>
         <v>0.46666666666666679</v>
       </c>
@@ -4191,17 +3886,17 @@
       <c r="D6" s="64"/>
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
-      <c r="J6" s="252" t="s">
-        <v>244</v>
-      </c>
-      <c r="L6" s="214" t="s">
-        <v>245</v>
+      <c r="J6" s="247" t="s">
+        <v>237</v>
+      </c>
+      <c r="L6" s="209" t="s">
+        <v>238</v>
       </c>
       <c r="N6"/>
-      <c r="O6" s="215" t="s">
-        <v>246</v>
-      </c>
-      <c r="P6" s="249">
+      <c r="O6" s="210" t="s">
+        <v>239</v>
+      </c>
+      <c r="P6" s="244">
         <f>1-P5</f>
         <v>0.53333333333333321</v>
       </c>
@@ -4209,8 +3904,8 @@
       <c r="R6"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="208" t="s">
-        <v>247</v>
+      <c r="A7" s="203" t="s">
+        <v>240</v>
       </c>
       <c r="B7" s="2">
         <v>0.12</v>
@@ -4223,8 +3918,8 @@
       <c r="R7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="208" t="s">
-        <v>248</v>
+      <c r="A8" s="203" t="s">
+        <v>241</v>
       </c>
       <c r="B8" s="2">
         <v>0.03</v>
@@ -4289,9 +3984,9 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="102"/>
       <c r="B17" t="s">
-        <v>249</v>
-      </c>
-      <c r="C17" s="216">
+        <v>242</v>
+      </c>
+      <c r="C17" s="211">
         <f>D3</f>
         <v>875</v>
       </c>
@@ -4303,7 +3998,7 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="102"/>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C18" s="102">
         <f>D4</f>
@@ -4329,9 +4024,9 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="102"/>
       <c r="B20" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" s="217">
+        <v>244</v>
+      </c>
+      <c r="C20" s="212">
         <f>H3</f>
         <v>0.21</v>
       </c>
@@ -4355,9 +4050,9 @@
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="102"/>
       <c r="B22" t="s">
-        <v>252</v>
-      </c>
-      <c r="C22" s="217">
+        <v>245</v>
+      </c>
+      <c r="C22" s="212">
         <f>H4</f>
         <v>0.14249999999999999</v>
       </c>
@@ -4381,9 +4076,9 @@
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="102"/>
       <c r="B25" t="s">
-        <v>253</v>
-      </c>
-      <c r="C25" s="218">
+        <v>246</v>
+      </c>
+      <c r="C25" s="213">
         <f>J4</f>
         <v>27.5625</v>
       </c>
@@ -4407,9 +4102,9 @@
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="102"/>
       <c r="B27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C27" s="218">
+        <v>247</v>
+      </c>
+      <c r="C27" s="213">
         <f>J3</f>
         <v>19.36</v>
       </c>
@@ -4444,7 +4139,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C31" s="12">
         <f>L3</f>
@@ -4453,7 +4148,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C32" t="str">
         <f>IF(M3&gt;0,"Over","Under")</f>
@@ -4462,7 +4157,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C33" s="12">
         <f>M3</f>
@@ -4471,7 +4166,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4479,7 +4174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DD48E3-D2F2-4CA7-B20E-1A62138DDEA3}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -4496,31 +4191,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="103" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
-      <c r="B4" s="219"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" s="219"/>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219"/>
-      <c r="H4" s="219"/>
-      <c r="I4" s="220"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="215"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="221" t="s">
-        <v>261</v>
+      <c r="A5" s="216" t="s">
+        <v>254</v>
       </c>
       <c r="B5" s="83">
         <v>0.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E5" s="126">
         <v>0</v>
@@ -4534,49 +4229,49 @@
       <c r="H5" s="18">
         <v>3</v>
       </c>
-      <c r="I5" s="222" t="s">
-        <v>263</v>
+      <c r="I5" s="217" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B6" s="91">
         <v>0.18</v>
       </c>
       <c r="D6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="223"/>
-      <c r="F6" s="199">
+        <v>258</v>
+      </c>
+      <c r="E6" s="218"/>
+      <c r="F6" s="194">
         <f>$B$5*(1+$B$6)^F5</f>
         <v>0.59</v>
       </c>
-      <c r="G6" s="199">
+      <c r="G6" s="194">
         <f>$B$5*(1+$B$6)^G5</f>
         <v>0.69619999999999993</v>
       </c>
-      <c r="H6" s="199">
+      <c r="H6" s="194">
         <f>$B$5*(1+$B$6)^H5</f>
         <v>0.82151599999999991</v>
       </c>
-      <c r="I6" s="224"/>
+      <c r="I6" s="219"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B7" s="90">
         <v>0.1</v>
       </c>
       <c r="D7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E7" s="196"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="I7" s="199">
+        <v>260</v>
+      </c>
+      <c r="E7" s="191"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="I7" s="194">
         <f>H6*(1+B7)/(B8-B7)</f>
         <v>45.183380000000021</v>
       </c>
@@ -4589,20 +4284,20 @@
         <v>0.12</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
-      </c>
-      <c r="E8" s="225">
+        <v>261</v>
+      </c>
+      <c r="E8" s="220">
         <f>NPV(B8,F6,G6,H6+I7)</f>
         <v>33.827168367346943</v>
       </c>
-      <c r="F8" s="198"/>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="193"/>
+      <c r="H8" s="193"/>
+      <c r="I8" s="193"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B9" s="104">
         <v>3</v>
@@ -4611,27 +4306,27 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
-      <c r="D10" s="219" t="s">
-        <v>270</v>
-      </c>
-      <c r="E10" s="226"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="219"/>
-      <c r="I10" s="220"/>
+      <c r="B10" s="214"/>
+      <c r="C10" s="214"/>
+      <c r="D10" s="214" t="s">
+        <v>263</v>
+      </c>
+      <c r="E10" s="221"/>
+      <c r="F10" s="214"/>
+      <c r="G10" s="214"/>
+      <c r="H10" s="214"/>
+      <c r="I10" s="215"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="221" t="s">
-        <v>261</v>
+      <c r="A11" s="216" t="s">
+        <v>254</v>
       </c>
       <c r="B11" s="12">
         <f>B5</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E11" s="126">
         <v>0</v>
@@ -4645,20 +4340,20 @@
       <c r="H11" s="18">
         <v>3</v>
       </c>
-      <c r="I11" s="227" t="s">
-        <v>263</v>
+      <c r="I11" s="222" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="221" t="s">
-        <v>264</v>
+      <c r="A12" s="216" t="s">
+        <v>257</v>
       </c>
       <c r="B12" s="1">
         <f>B6</f>
         <v>0.18</v>
       </c>
       <c r="D12" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E12" s="65"/>
       <c r="F12" s="12">
@@ -4676,24 +4371,24 @@
       <c r="I12" s="58"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="221" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="228">
+      <c r="A13" s="216" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="223">
         <f>B7</f>
         <v>0.1</v>
       </c>
       <c r="D13" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E13" s="64"/>
-      <c r="I13" s="229">
+      <c r="I13" s="224">
         <f>(H12*(1+B13))/(B14-B13)</f>
         <v>45.183380000000021</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="221" t="s">
+      <c r="A14" s="216" t="s">
         <v>124</v>
       </c>
       <c r="B14" s="1">
@@ -4703,37 +4398,37 @@
       <c r="D14" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="230"/>
-      <c r="F14" s="231">
+      <c r="E14" s="225"/>
+      <c r="F14" s="226">
         <f>F12/((1+$B$8)^F5)</f>
         <v>0.52678571428571419</v>
       </c>
-      <c r="G14" s="231">
+      <c r="G14" s="226">
         <f>G12/((1+$B$8)^G5)</f>
         <v>0.55500637755102022</v>
       </c>
-      <c r="H14" s="231">
+      <c r="H14" s="226">
         <f>H12/((1+$B$8)^H5)</f>
         <v>0.584738862062682</v>
       </c>
-      <c r="I14" s="232">
+      <c r="I14" s="227">
         <f>I13/((1+$B$8)^H11)</f>
         <v>32.160637413447525</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="233">
+        <v>262</v>
+      </c>
+      <c r="B15" s="228">
         <f>B9</f>
         <v>3</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="E15" s="234">
+        <v>261</v>
+      </c>
+      <c r="E15" s="229">
         <f>SUM(F14:I14)</f>
         <v>33.827168367346943</v>
       </c>
@@ -4804,7 +4499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AC71B9-F875-4331-AD1C-C4F77D609F2B}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -4951,7 +4646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B053C31B-F6B7-4D1D-8C6B-72374219DA74}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -4965,7 +4660,7 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B3" s="10">
         <v>15000</v>
@@ -4976,26 +4671,26 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B6" s="12">
         <v>42.88</v>
       </c>
-      <c r="C6" s="245">
+      <c r="C6" s="240">
         <v>0.3</v>
       </c>
       <c r="D6" s="10">
@@ -5013,12 +4708,12 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B7" s="12">
         <v>51.32</v>
       </c>
-      <c r="C7" s="245">
+      <c r="C7" s="240">
         <v>0.4</v>
       </c>
       <c r="D7" s="10">
@@ -5036,12 +4731,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B8" s="12">
         <v>8.51</v>
       </c>
-      <c r="C8" s="245">
+      <c r="C8" s="240">
         <v>0.3</v>
       </c>
       <c r="D8" s="10">
@@ -5062,7 +4757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748E5A36-5034-488B-AEF2-31F710CDEA28}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -5075,7 +4770,7 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C2">
         <v>500</v>
@@ -5083,7 +4778,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C3" s="12">
         <v>103.39</v>
@@ -5091,7 +4786,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C4" s="144">
         <v>0.35</v>
@@ -5099,7 +4794,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C5" s="12">
         <v>106.69</v>
@@ -5107,7 +4802,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C7" s="12">
         <f>((C5-C3)+C4)*C2</f>
@@ -5116,7 +4811,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C8" s="11">
         <f>C7/(C3*C2)</f>
@@ -5128,7 +4823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB18100-7802-47A4-927A-CF793B15C087}">
   <sheetPr>
     <tabColor rgb="FFEE0000"/>
@@ -5142,22 +4837,22 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B5" s="10">
         <v>30000</v>
@@ -5169,7 +4864,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="236" t="str">
+      <c r="A8" s="231" t="str">
         <f>TEXT(A3,"")&amp; " is considering buying "&amp;TEXT(A4,"")&amp;" that will generate perpetual after-tax cash flows of "&amp;TEXT(B27,"$0,000")&amp;" per year beginning next year."</f>
         <v>Big Firm is considering buying Small Firm that will generate perpetual after-tax cash flows of $30,000 per year beginning next year.</v>
       </c>
@@ -5193,38 +4888,38 @@
       <c r="S8" s="57"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="235" t="s">
-        <v>283</v>
+      <c r="A9" s="230" t="s">
+        <v>276</v>
       </c>
       <c r="S9" s="58"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="235" t="str">
+      <c r="A10" s="230" t="str">
         <f>"Cost of Equity including flotation costs is " &amp;TEXT( B21,"0.00%") &amp;" and debt issues cost "&amp;TEXT(B22,"0.00%") &amp;" on an after-tax basis."</f>
         <v>Cost of Equity including flotation costs is 15.00% and debt issues cost 5.00% on an after-tax basis.</v>
       </c>
       <c r="S10" s="58"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="235" t="str">
+      <c r="A11" s="230" t="str">
         <f>"The current capital structure is " &amp;TEXT(B16,"0.00%")&amp; " debt and "&amp;TEXT(B17,"0.00%") &amp;" equity."</f>
         <v>The current capital structure is 30.00% debt and 70.00% equity.</v>
       </c>
       <c r="S11" s="58"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="235"/>
+      <c r="A12" s="230"/>
       <c r="S12" s="58"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="235" t="s">
-        <v>284</v>
+      <c r="A13" s="230" t="s">
+        <v>277</v>
       </c>
       <c r="S13" s="58"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="235" t="s">
-        <v>285</v>
+      <c r="A14" s="230" t="s">
+        <v>278</v>
       </c>
       <c r="S14" s="58"/>
     </row>
@@ -5262,14 +4957,14 @@
       <c r="A17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="237">
+      <c r="B17" s="232">
         <v>0.7</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B18" s="2">
         <f>B16+B17</f>
@@ -5278,7 +4973,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B21" s="2">
         <v>0.15</v>
@@ -5286,24 +4981,24 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B22" s="1">
         <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="238" t="s">
-        <v>289</v>
-      </c>
-      <c r="B24" s="239">
+      <c r="A24" s="233" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="234">
         <f>(B21*B17)+(B22*B16)</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B27" s="10">
         <v>30000</v>
@@ -5311,16 +5006,213 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="238" t="s">
-        <v>292</v>
-      </c>
-      <c r="B31" s="240">
+      <c r="A31" s="233" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="235">
         <f>B27/B24</f>
         <v>250000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9458BEA2-912B-4733-9C99-A8EEABC3ED6D}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="216"/>
+      <c r="B5" s="15"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="15"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="230" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="230" t="str">
+        <f>"What is "&amp;TEXT(B3,"0.00%") &amp;" cost of equity using retained earnings?"</f>
+        <v>What is IBM Corp cost of equity using retained earnings?</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" s="21">
+        <f>B13+B12*(B14-B13)</f>
+        <v>0.16499999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="248" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="57"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="249" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="250"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
+      <c r="B26" s="167"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="251">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="252"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="165" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="170">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="165" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="170">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="165" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="170">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="165" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="167">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="216" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="253">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="216"/>
+      <c r="B34" s="58"/>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="254" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="222"/>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="216" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="255">
+        <f>B30+B32*(B31-B30)</f>
+        <v>0.16499999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -5553,203 +5445,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9458BEA2-912B-4733-9C99-A8EEABC3ED6D}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="221"/>
-      <c r="B5" s="15"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="15"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="235" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="235" t="str">
-        <f>"What is "&amp;TEXT(B3,"0.00%") &amp;" cost of equity using retained earnings?"</f>
-        <v>What is IBM Corp cost of equity using retained earnings?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B10" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>277</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="B16" s="21">
-        <f>B13+B12*(B14-B13)</f>
-        <v>0.16499999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="253" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="57"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="254" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="255"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="170"/>
-      <c r="B26" s="172"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="254" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="256">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="257"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="170" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="175">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="170" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="175">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="170" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="175">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="172">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="221" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="258">
-        <v>0.155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="221"/>
-      <c r="B34" s="58"/>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="259" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="227"/>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="221" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="260">
-        <f>B30+B32*(B31-B30)</f>
-        <v>0.16499999999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C25BF6-CC9C-4D8E-AB7A-1878F58DAAAE}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -5781,18 +5476,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="E2" s="253" t="s">
+      <c r="E2" s="248" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="57"/>
-      <c r="H2" s="253" t="s">
+      <c r="H2" s="248" t="s">
         <v>3</v>
       </c>
       <c r="I2" s="57"/>
-      <c r="K2" s="290" t="s">
+      <c r="K2" s="285" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="291"/>
+      <c r="L2" s="286"/>
       <c r="M2" s="56"/>
       <c r="N2" s="56"/>
       <c r="O2" s="57"/>
@@ -5809,24 +5504,24 @@
         <f t="shared" ref="C3:C9" ca="1" si="0">_xlfn.FORMULATEXT(B3)</f>
         <v>=F17</v>
       </c>
-      <c r="E3" s="254" t="s">
+      <c r="E3" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="255">
+      <c r="F3" s="250">
         <v>550000</v>
       </c>
       <c r="G3" s="13"/>
-      <c r="H3" s="254" t="s">
+      <c r="H3" s="249" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="267">
+      <c r="I3" s="262">
         <v>100000</v>
       </c>
       <c r="J3" s="13"/>
-      <c r="K3" s="272" t="s">
+      <c r="K3" s="267" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="273">
+      <c r="L3" s="268">
         <v>21000000</v>
       </c>
       <c r="O3" s="58"/>
@@ -5843,13 +5538,13 @@
         <f t="shared" ca="1" si="0"/>
         <v>=F28</v>
       </c>
-      <c r="E4" s="170"/>
-      <c r="F4" s="172"/>
+      <c r="E4" s="165"/>
+      <c r="F4" s="167"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="172"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="167"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="170" t="s">
+      <c r="K4" s="165" t="s">
         <v>10</v>
       </c>
       <c r="L4" s="142">
@@ -5869,21 +5564,21 @@
         <f t="shared" ca="1" si="0"/>
         <v>=I14</v>
       </c>
-      <c r="E5" s="254" t="s">
+      <c r="E5" s="249" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="256">
+      <c r="F5" s="251">
         <v>45</v>
       </c>
       <c r="G5" s="13"/>
-      <c r="H5" s="254" t="s">
+      <c r="H5" s="249" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="256">
+      <c r="I5" s="251">
         <v>52</v>
       </c>
       <c r="J5" s="13"/>
-      <c r="K5" s="170" t="s">
+      <c r="K5" s="165" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="13">
@@ -5903,24 +5598,24 @@
         <f t="shared" ca="1" si="0"/>
         <v>=I22</v>
       </c>
-      <c r="E6" s="170" t="s">
+      <c r="E6" s="165" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="257">
+      <c r="F6" s="252">
         <v>3</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="170" t="s">
+      <c r="H6" s="165" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="257">
+      <c r="I6" s="252">
         <v>4</v>
       </c>
       <c r="J6" s="13"/>
-      <c r="K6" s="170" t="s">
+      <c r="K6" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="274">
+      <c r="L6" s="269">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="O6" s="58"/>
@@ -5937,21 +5632,21 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L14</v>
       </c>
-      <c r="E7" s="170" t="s">
+      <c r="E7" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="175">
+      <c r="F7" s="170">
         <v>0.06</v>
       </c>
       <c r="G7" s="13"/>
-      <c r="H7" s="170" t="s">
+      <c r="H7" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="268">
+      <c r="I7" s="263">
         <v>0.1</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="170" t="s">
+      <c r="K7" s="165" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="83">
@@ -5972,17 +5667,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L10</v>
       </c>
-      <c r="E8" s="170" t="s">
+      <c r="E8" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="175">
+      <c r="F8" s="170">
         <v>0.03</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="170"/>
-      <c r="I8" s="172"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="167"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="170" t="s">
+      <c r="K8" s="165" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="13">
@@ -6002,39 +5697,39 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L17</v>
       </c>
-      <c r="E9" s="170" t="s">
+      <c r="E9" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="175">
+      <c r="F9" s="170">
         <v>0.1</v>
       </c>
       <c r="G9" s="13"/>
-      <c r="H9" s="170"/>
-      <c r="I9" s="172"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="254" t="s">
+      <c r="K9" s="249" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="275">
+      <c r="L9" s="270">
         <v>0.98499999999999999</v>
       </c>
       <c r="O9" s="58"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E10" s="170" t="s">
+      <c r="E10" s="165" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="172">
+      <c r="F10" s="167">
         <v>1.4</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="170"/>
-      <c r="I10" s="172"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="13"/>
-      <c r="K10" s="170" t="s">
+      <c r="K10" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="274">
+      <c r="L10" s="269">
         <v>0.21</v>
       </c>
       <c r="O10" s="58"/>
@@ -6051,15 +5746,15 @@
         <f t="shared" ref="C11:C18" ca="1" si="1">_xlfn.FORMULATEXT(B11)</f>
         <v>=F3</v>
       </c>
-      <c r="E11" s="221" t="s">
+      <c r="E11" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="258">
+      <c r="F11" s="253">
         <v>0.2</v>
       </c>
-      <c r="H11" s="221"/>
+      <c r="H11" s="216"/>
       <c r="I11" s="58"/>
-      <c r="K11" s="221"/>
+      <c r="K11" s="216"/>
       <c r="O11" s="58"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -6074,11 +5769,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>=F5</v>
       </c>
-      <c r="E12" s="221"/>
+      <c r="E12" s="216"/>
       <c r="F12" s="58"/>
-      <c r="H12" s="221"/>
+      <c r="H12" s="216"/>
       <c r="I12" s="58"/>
-      <c r="K12" s="221" t="s">
+      <c r="K12" s="216" t="s">
         <v>28</v>
       </c>
       <c r="L12" s="12">
@@ -6099,15 +5794,15 @@
         <f t="shared" ca="1" si="1"/>
         <v>=I3</v>
       </c>
-      <c r="E13" s="259" t="s">
+      <c r="E13" s="254" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="227"/>
-      <c r="H13" s="259" t="s">
+      <c r="F13" s="222"/>
+      <c r="H13" s="254" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="58"/>
-      <c r="K13" s="221"/>
+      <c r="K13" s="216"/>
       <c r="L13" s="12"/>
       <c r="O13" s="58"/>
     </row>
@@ -6123,17 +5818,17 @@
         <f t="shared" ca="1" si="1"/>
         <v>=I5</v>
       </c>
-      <c r="E14" s="221" t="s">
+      <c r="E14" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="260">
+      <c r="F14" s="255">
         <f>F8+F10*(F9-F8)</f>
         <v>0.128</v>
       </c>
-      <c r="H14" s="269" t="s">
+      <c r="H14" s="264" t="s">
         <v>154</v>
       </c>
-      <c r="I14" s="248">
+      <c r="I14" s="243">
         <f>I6/I5</f>
         <v>7.6923076923076927E-2</v>
       </c>
@@ -6161,16 +5856,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L9</v>
       </c>
-      <c r="E15" s="221" t="s">
+      <c r="E15" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="260">
+      <c r="F15" s="255">
         <f>F6/F5+F7</f>
         <v>0.12666666666666665</v>
       </c>
-      <c r="H15" s="221"/>
+      <c r="H15" s="216"/>
       <c r="I15" s="58"/>
-      <c r="K15" s="221"/>
+      <c r="K15" s="216"/>
       <c r="M15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(L14)</f>
         <v>=L8*RATE(L5*L8,(-L7/L8),L12,-L4)</v>
@@ -6189,11 +5884,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L3</v>
       </c>
-      <c r="E16" s="221"/>
+      <c r="E16" s="216"/>
       <c r="F16" s="58"/>
-      <c r="H16" s="221"/>
+      <c r="H16" s="216"/>
       <c r="I16" s="58"/>
-      <c r="K16" s="221"/>
+      <c r="K16" s="216"/>
       <c r="O16" s="58"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -6208,19 +5903,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L4</v>
       </c>
-      <c r="E17" s="261" t="s">
+      <c r="E17" s="256" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="262">
+      <c r="F17" s="257">
         <f>AVERAGE(F14:F15)</f>
         <v>0.12733333333333333</v>
       </c>
-      <c r="H17" s="221"/>
+      <c r="H17" s="216"/>
       <c r="I17" s="58"/>
       <c r="K17" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="276">
+      <c r="L17" s="271">
         <f>L14*(1-L10)</f>
         <v>6.8261805524100397E-2</v>
       </c>
@@ -6241,20 +5936,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>=B15*B17</v>
       </c>
-      <c r="E18" s="221"/>
+      <c r="E18" s="216"/>
       <c r="F18" s="58"/>
-      <c r="H18" s="221"/>
+      <c r="H18" s="216"/>
       <c r="I18" s="58"/>
-      <c r="K18" s="221"/>
+      <c r="K18" s="216"/>
       <c r="O18" s="58"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" s="26"/>
-      <c r="E19" s="221"/>
+      <c r="E19" s="216"/>
       <c r="F19" s="58"/>
-      <c r="H19" s="221"/>
+      <c r="H19" s="216"/>
       <c r="I19" s="58"/>
-      <c r="K19" s="221"/>
+      <c r="K19" s="216"/>
       <c r="O19" s="58"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6262,15 +5957,15 @@
         <v>41</v>
       </c>
       <c r="B20" s="28"/>
-      <c r="E20" s="259" t="s">
+      <c r="E20" s="254" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="227"/>
-      <c r="H20" s="259" t="s">
+      <c r="F20" s="222"/>
+      <c r="H20" s="254" t="s">
         <v>43</v>
       </c>
       <c r="I20" s="58"/>
-      <c r="K20" s="221" t="s">
+      <c r="K20" s="216" t="s">
         <v>44</v>
       </c>
       <c r="O20" s="58"/>
@@ -6287,17 +5982,17 @@
         <f ca="1">_xlfn.FORMULATEXT(B21)</f>
         <v>=B11*B12</v>
       </c>
-      <c r="E21" s="221" t="s">
+      <c r="E21" s="216" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="263">
+      <c r="F21" s="258">
         <f>F5*F11</f>
         <v>9</v>
       </c>
-      <c r="H21" s="221" t="s">
+      <c r="H21" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="270">
+      <c r="I21" s="265">
         <f>I7*I5</f>
         <v>5.2</v>
       </c>
@@ -6321,17 +6016,17 @@
         <f ca="1">_xlfn.FORMULATEXT(B22)</f>
         <v>=B13*B14</v>
       </c>
-      <c r="E22" s="264" t="s">
+      <c r="E22" s="259" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="265">
+      <c r="F22" s="260">
         <f>F6/(F5-F21)+F7</f>
         <v>0.14333333333333331</v>
       </c>
-      <c r="H22" s="271" t="s">
+      <c r="H22" s="266" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="277">
+      <c r="I22" s="272">
         <f>I6/(I5-I21)</f>
         <v>8.5470085470085472E-2</v>
       </c>
@@ -6348,7 +6043,7 @@
         <f ca="1">_xlfn.FORMULATEXT(B23)</f>
         <v>=B16*B15</v>
       </c>
-      <c r="E23" s="221"/>
+      <c r="E23" s="216"/>
       <c r="F23" s="58"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -6359,17 +6054,17 @@
         <f>SUM(B21:B23)</f>
         <v>50635000</v>
       </c>
-      <c r="E24" s="221" t="s">
+      <c r="E24" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="260">
+      <c r="F24" s="255">
         <f>F22-F15</f>
         <v>1.6666666666666663E-2</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="33"/>
-      <c r="E25" s="221"/>
+      <c r="E25" s="216"/>
       <c r="F25" s="58"/>
     </row>
     <row r="26" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6377,10 +6072,10 @@
         <v>55</v>
       </c>
       <c r="B26" s="34"/>
-      <c r="E26" s="221" t="s">
+      <c r="E26" s="216" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="260">
+      <c r="F26" s="255">
         <f>F14+F24</f>
         <v>0.14466666666666667</v>
       </c>
@@ -6397,7 +6092,7 @@
         <f ca="1">_xlfn.FORMULATEXT(B27)</f>
         <v>=B21/$B$24</v>
       </c>
-      <c r="E27" s="221"/>
+      <c r="E27" s="216"/>
       <c r="F27" s="58"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -6412,10 +6107,10 @@
         <f ca="1">_xlfn.FORMULATEXT(B28)</f>
         <v>=B22/$B$24</v>
       </c>
-      <c r="E28" s="266" t="s">
+      <c r="E28" s="261" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="278">
+      <c r="F28" s="273">
         <f>AVERAGE(F26,F22)</f>
         <v>0.14399999999999999</v>
       </c>
@@ -6729,8 +6424,8 @@
       <c r="A1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
       <c r="G1" s="30"/>
       <c r="H1" s="30"/>
       <c r="I1" s="30"/>
@@ -6945,7 +6640,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6953,12 +6648,12 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B5" s="142">
         <v>5000</v>
@@ -6982,16 +6677,16 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="244">
+        <v>288</v>
+      </c>
+      <c r="B9" s="239">
         <f xml:space="preserve"> NPER(B7,0,B5,-B6)</f>
         <v>8.0432317269320457</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B11">
         <f>72/9</f>
@@ -7016,23 +6711,23 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B3" s="280">
+        <v>311</v>
+      </c>
+      <c r="B3" s="275">
         <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B4" s="280">
+        <v>312</v>
+      </c>
+      <c r="B4" s="275">
         <v>150000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -7048,7 +6743,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B7">
         <f>B5*B6</f>
@@ -7059,7 +6754,7 @@
       <c r="A9" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="279">
+      <c r="B9" s="274">
         <f>RATE(B7,-B3,0,B4)*12</f>
         <v>1.3711616116975691E-2</v>
       </c>
@@ -7086,27 +6781,27 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="283" t="s">
-        <v>322</v>
-      </c>
-      <c r="B3" s="284"/>
-      <c r="C3" s="284"/>
-      <c r="D3" s="284"/>
-      <c r="E3" s="284"/>
+      <c r="A3" s="278" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="279"/>
+      <c r="C3" s="279"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="281">
+      <c r="B6" s="276">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>319</v>
-      </c>
-      <c r="B7" s="281">
+        <v>312</v>
+      </c>
+      <c r="B7" s="276">
         <v>10000</v>
       </c>
     </row>
@@ -7120,9 +6815,9 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>323</v>
-      </c>
-      <c r="B10" s="282">
+        <v>316</v>
+      </c>
+      <c r="B10" s="277">
         <f>NPER(B8,0,B6,-B7)</f>
         <v>8.0432317269320457</v>
       </c>
@@ -7285,7 +6980,7 @@
         <v>100</v>
       </c>
       <c r="I1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
@@ -7301,7 +6996,7 @@
         <v>14.5</v>
       </c>
       <c r="I2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -7327,7 +7022,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -7356,7 +7051,7 @@
         <v>0.03</v>
       </c>
       <c r="I6" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -7629,141 +7324,269 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF3C513-AC45-4926-AE9B-82A3755882B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93BCCDF-AEB1-4B38-A1E0-2C0745BFEA03}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.499984740745262"/>
+    <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
-        <f>" The starting dollar value of  a bond is " &amp; TEXT(C8,"$0,000.00")&amp;" If the yield on the bond rises from " &amp; TEXT(C10,"0.00%") &amp;" to " &amp;TEXT(C11,"0.00%")&amp; ", and the ending dollar value of the bond is " &amp; TEXT(C9,"$000.00")</f>
-        <v xml:space="preserve"> The starting dollar value of  a bond is $1,100.00 If the yield on the bond rises from 3.00% to 5.00%, and the ending dollar value of the bond is $950.00</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="85">
-        <f>C14</f>
-        <v>6.8181818181818175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="64" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="284" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27" t="s">
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+    </row>
+    <row r="2" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="283" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="B2" s="283"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="283" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="B3" s="283"/>
+      <c r="C3" s="283"/>
+      <c r="D3" s="283"/>
+      <c r="E3" s="283"/>
+      <c r="F3" s="283"/>
+      <c r="G3" s="283"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="161">
-        <v>1100</v>
-      </c>
-      <c r="D8" s="84">
-        <f>C8/1000</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="B4" s="283"/>
+      <c r="C4" s="283"/>
+      <c r="D4" s="283"/>
+      <c r="E4" s="283"/>
+      <c r="F4" s="283"/>
+      <c r="G4" s="283"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="283" t="s">
         <v>198</v>
       </c>
-      <c r="C9" s="162">
-        <v>950</v>
-      </c>
-      <c r="D9" s="84">
-        <f t="shared" ref="D9" si="0">C9/1000</f>
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="B5" s="283"/>
+      <c r="C5" s="283"/>
+      <c r="D5" s="283"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="283"/>
+      <c r="G5" s="283"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="283" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="163">
-        <v>0.03</v>
-      </c>
-      <c r="D10" s="164">
-        <f>C10</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="B6" s="283"/>
+      <c r="C6" s="283"/>
+      <c r="D6" s="283"/>
+      <c r="E6" s="283"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="161"/>
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="163">
-        <v>0.05</v>
-      </c>
-      <c r="D11" s="164">
-        <f>C11</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="65">
-        <f>C9-C8</f>
-        <v>-150</v>
-      </c>
-      <c r="D12" s="84">
-        <f>D9-D8</f>
-        <v>-0.15000000000000013</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="84">
-        <f>C11-C10</f>
-        <v>2.0000000000000004E-2</v>
-      </c>
-      <c r="D13" s="84">
-        <f>D11-D10</f>
-        <v>2.0000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="165">
-        <f>-C12/(C8*C13)</f>
-        <v>6.8181818181818175</v>
-      </c>
-      <c r="D14" s="165">
-        <f>-D12/(D8*D13)</f>
-        <v>6.8181818181818228</v>
+      <c r="B8" s="162">
+        <v>0.98450000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="163" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="164">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="165" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="166">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="165" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="167">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="168" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="165" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="170">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="171" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="172">
+        <f>B13*B10</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="5">
+        <f>B11*2</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="5">
+        <f>B12*2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="173">
+        <f>B14/2</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="12">
+        <f>B8*B10</f>
+        <v>984.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="12">
+        <f>B14</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" s="12">
+        <f>B21+B10</f>
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" s="174">
+        <f>B14/B20</f>
+        <v>4.5708481462671403E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="175">
+        <f>RATE(B16,-B18,B20,-B10)</f>
+        <v>2.3223120114168081E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B27" s="66">
+        <f>B26*2</f>
+        <v>4.6446240228336162E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" s="175">
+        <f>RATE(B17,-B18,B20,-B22)</f>
+        <v>2.8257927444819992E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30" s="66">
+        <f>B29*2</f>
+        <v>5.6515854889639984E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="176">
+        <f>B27/(1-B9)</f>
+        <v>7.2572250356775253E-2</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
+++ b/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/Documents/GitHub/BUS210---Final-Exam-Practice-Problems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8A322C-9C37-40D2-825F-6AE31DEE0053}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E0160D-A0EB-4240-80F0-41C09842B861}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TVM #1-15" sheetId="19" r:id="rId1"/>
@@ -22,17 +22,15 @@
     <sheet name="Bond #1-20" sheetId="21" r:id="rId7"/>
     <sheet name="Bond #2-19" sheetId="22" r:id="rId8"/>
     <sheet name="Bond #4-18" sheetId="24" r:id="rId9"/>
-    <sheet name="Bond #5-16" sheetId="16" r:id="rId10"/>
-    <sheet name="Bond #6-14" sheetId="33" r:id="rId11"/>
-    <sheet name="Equity #1-1" sheetId="25" r:id="rId12"/>
-    <sheet name="Equity #2-3" sheetId="26" r:id="rId13"/>
-    <sheet name="Equity #3-4" sheetId="27" r:id="rId14"/>
-    <sheet name="Equity #4-5" sheetId="15" r:id="rId15"/>
-    <sheet name="Equity #5-12" sheetId="30" r:id="rId16"/>
-    <sheet name="Equity #6-13" sheetId="31" r:id="rId17"/>
-    <sheet name="WACC #1-6" sheetId="17" r:id="rId18"/>
-    <sheet name="WACC #2-7" sheetId="28" r:id="rId19"/>
-    <sheet name="WACC #3-17" sheetId="2" r:id="rId20"/>
+    <sheet name="Equity #1-1" sheetId="25" r:id="rId10"/>
+    <sheet name="Equity #2-3" sheetId="26" r:id="rId11"/>
+    <sheet name="Equity #3-4" sheetId="27" r:id="rId12"/>
+    <sheet name="Equity #4-5" sheetId="15" r:id="rId13"/>
+    <sheet name="Equity #5-12" sheetId="30" r:id="rId14"/>
+    <sheet name="Equity #6-13" sheetId="31" r:id="rId15"/>
+    <sheet name="WACC #1-6" sheetId="17" r:id="rId16"/>
+    <sheet name="WACC #2-7" sheetId="28" r:id="rId17"/>
+    <sheet name="WACC #3-17" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -55,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="295">
   <si>
     <t>Beta</t>
   </si>
@@ -363,45 +361,15 @@
     <t>Coupon</t>
   </si>
   <si>
-    <t>∆P</t>
-  </si>
-  <si>
-    <t>∆Y</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>Par Value</t>
   </si>
   <si>
     <t>S/A Yield</t>
   </si>
   <si>
-    <t>Starting</t>
-  </si>
-  <si>
     <t>Ending</t>
   </si>
   <si>
-    <t>Corp Bond Maturity</t>
-  </si>
-  <si>
-    <t>Annual Coupon Payment</t>
-  </si>
-  <si>
-    <t>S/Acoupon Payment</t>
-  </si>
-  <si>
-    <t>Credit Spread</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YTM </t>
-  </si>
-  <si>
-    <t>Quoted bond price</t>
-  </si>
-  <si>
     <t>Linked EPS &amp; DPS Problem</t>
   </si>
   <si>
@@ -483,79 +451,7 @@
     <t>What is the EAR on the Master card?</t>
   </si>
   <si>
-    <t>What is the yield to maturity of the bond?</t>
-  </si>
-  <si>
-    <t>What is the bonds $$ value?</t>
-  </si>
-  <si>
-    <t>What is the bonds quoted price?</t>
-  </si>
-  <si>
-    <t>What is the yield are you selling the bond at?</t>
-  </si>
-  <si>
-    <t>What is the bonds quoted price at the time of the sale?</t>
-  </si>
-  <si>
-    <t>What is the price change of the bond from purchase to sale?</t>
-  </si>
-  <si>
-    <t>What is the duration of the bond?</t>
-  </si>
-  <si>
     <t>N -Years until Div Iniations (D1)</t>
-  </si>
-  <si>
-    <t>Bond Value $$$</t>
-  </si>
-  <si>
-    <t>What is the bonds $$ value at the time of the sale?</t>
-  </si>
-  <si>
-    <r>
-      <t>D=-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>P/((P_0*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y)</t>
-    </r>
   </si>
   <si>
     <t>Year</t>
@@ -974,9 +870,6 @@
     <t>PV of small company - most pay for</t>
   </si>
   <si>
-    <t>Treasury Yield</t>
-  </si>
-  <si>
     <t>Beginning</t>
   </si>
   <si>
@@ -992,21 +885,6 @@
     <t>Rule of 72</t>
   </si>
   <si>
-    <t>US Treasury</t>
-  </si>
-  <si>
-    <t>A3/AA- Corp</t>
-  </si>
-  <si>
-    <t>A2/AA Muni</t>
-  </si>
-  <si>
-    <t>Your client is in the 36% tax bracket. You are evaluating 3 different bond offering all having a 10year maturity</t>
-  </si>
-  <si>
-    <t>Spread</t>
-  </si>
-  <si>
     <t>Fed EX Share</t>
   </si>
   <si>
@@ -1043,12 +921,6 @@
     <t>Approx</t>
   </si>
   <si>
-    <t>a Tsy, Corp and a muni</t>
-  </si>
-  <si>
-    <t>Raw Yield</t>
-  </si>
-  <si>
     <t>Pmt</t>
   </si>
   <si>
@@ -1080,6 +952,9 @@
   </si>
   <si>
     <t xml:space="preserve">A 15 year bond with semi-annual coupons payments, with a 6.00% coupon rate is valued at a bond $$ value $1,000 </t>
+  </si>
+  <si>
+    <t>Create the amortization schedule for your new car loan of $25,000, paid monthly over 5 years using an 8.00% APR.</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +972,7 @@
     <numFmt numFmtId="167" formatCode="0.000%"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1246,28 +1121,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color rgb="FF002E60"/>
       <name val="Calibri"/>
@@ -1355,7 +1208,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1410,14 +1263,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1674,30 +1521,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1786,7 +1609,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1955,13 +1778,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2002,27 +1819,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2030,7 +1828,7 @@
     <xf numFmtId="8" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="8" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2039,38 +1837,38 @@
     <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2079,8 +1877,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2090,33 +1888,33 @@
     <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
@@ -2129,17 +1927,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="6" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2159,18 +1957,18 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="8" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
@@ -2185,10 +1983,10 @@
     <xf numFmtId="8" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2196,26 +1994,20 @@
     <xf numFmtId="10" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="33" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="30" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="44" fontId="33" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="30" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2259,8 +2051,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2270,7 +2062,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2300,64 +2092,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9696C955-251C-41C0-9C99-ACECE7D0260E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1819275" y="3028950"/>
-          <a:ext cx="9525" cy="476250"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2641,31 +2375,31 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="122" t="str">
+      <c r="A3" s="118" t="str">
         <f>"You must choose between a " &amp;TEXT(B9,"")&amp; " credit card charging an APR of " &amp;TEXT(B10,"0.00%")&amp; " with daily compounding or a " &amp;TEXT(C9,"")&amp;" with an APR of "&amp;TEXT(C10,"0.00%") &amp;"with monthly compounding."</f>
         <v>You must choose between a Visa credit card charging an APR of 18.25% with daily compounding or a Master Card with an APR of 19.00%with monthly compounding.</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="122" t="s">
-        <v>140</v>
+      <c r="A4" s="118" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="280" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="281"/>
+      <c r="B8" s="261" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="262"/>
     </row>
     <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="71" t="s">
@@ -2705,7 +2439,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="77" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2747,7 +2481,7 @@
         <v>98</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,19 +2490,19 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A19" s="143" t="str">
+      <c r="A19" s="126" t="str">
         <f>"Now assume you have "&amp; TEXT(B22,"$0,000") &amp; " credit outstanding (loan balance) on the Visa credit card at the beginning of the year."</f>
         <v>Now assume you have $5,000 credit outstanding (loan balance) on the Visa credit card at the beginning of the year.</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A20" s="143" t="s">
-        <v>157</v>
+      <c r="A20" s="126" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B22" s="10">
         <v>5000</v>
@@ -2776,7 +2510,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B23" s="12">
         <f>B22*B14</f>
@@ -2789,7 +2523,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B24" s="12">
         <f>B23+B22</f>
@@ -2812,430 +2546,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D61A856-DAAF-457A-805A-BE6676D4C18E}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="str">
-        <f>"You have decided to purchase a "&amp;TEXT(J6,"0.00%")&amp; " corporate bond with years left until maturity of "&amp; TEXT(J7,"0")</f>
-        <v>You have decided to purchase a 6.00% corporate bond with years left until maturity of 10</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="J2" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="K2" s="64" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="str">
-        <f>"The default/credit spread of the bond offering is " &amp;TEXT(J12*10000,"0")&amp;" basis points over the comparable maturity Treasury"</f>
-        <v>The default/credit spread of the bond offering is 100 basis points over the comparable maturity Treasury</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="J3" s="126" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="str">
-        <f>"The comperable US Treasury currently yields " &amp; TEXT(J11,"0.00%")</f>
-        <v>The comperable US Treasury currently yields 5.00%</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="I4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J4" s="132">
-        <v>1000</v>
-      </c>
-      <c r="K4" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="127">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="I6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J6" s="128">
-        <v>0.06</v>
-      </c>
-      <c r="K6" s="11">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="I7" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="127">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="I8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J8" s="129">
-        <f>J6*J4</f>
-        <v>60</v>
-      </c>
-      <c r="K8" s="12">
-        <f>K6*K4</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J9" s="129">
-        <f>J8/2</f>
-        <v>30</v>
-      </c>
-      <c r="K9" s="12">
-        <f>K8/2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J10" s="127"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
-        <f>TEXT(J7-K7,"0.0") &amp;" year(s) later, you decide to sell the bond"</f>
-        <v>1.0 year(s) later, you decide to sell the bond</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="I11" t="s">
-        <v>286</v>
-      </c>
-      <c r="J11" s="130">
-        <v>0.05</v>
-      </c>
-      <c r="K11" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="str">
-        <f>"The comparable maturity US Tsy now yields " &amp; TEXT(K11,"0.00%")</f>
-        <v>The comparable maturity US Tsy now yields 4.50%</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="I12" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="131">
-        <v>0.01</v>
-      </c>
-      <c r="K12" s="87">
-        <v>1.2500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
-        <f>"The bid/selling level credit spread of the bond is " &amp;TEXT(K12*10000,"0")&amp;" basis points over the comparable maturity Treasury"</f>
-        <v>The bid/selling level credit spread of the bond is 125 basis points over the comparable maturity Treasury</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="I13" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="133">
-        <f>J11+J12</f>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="K13" s="2">
-        <f>SUM(K11:K12)</f>
-        <v>5.7499999999999996E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J14" s="127"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="I15" t="s">
-        <v>106</v>
-      </c>
-      <c r="J15" s="130">
-        <f>J13/J5</f>
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="K15" s="2">
-        <f>K13/K5</f>
-        <v>2.8749999999999998E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="12"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="I17" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="134">
-        <f>PV(J15,J7*J5,-J9,-J4)</f>
-        <v>999.99999999999989</v>
-      </c>
-      <c r="K17" s="12">
-        <f>PV(K15,K7*K5,-K9,-K4)</f>
-        <v>1017.3749920428743</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="I18" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="135">
-        <f>J17/J4</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="K18" s="124">
-        <f>K17/K4</f>
-        <v>1.0173749920428743</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="85"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J20" s="2"/>
-      <c r="K20" t="s">
-        <v>102</v>
-      </c>
-      <c r="L20" s="123">
-        <f>K17-J17</f>
-        <v>17.374992042874396</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K21" t="s">
-        <v>103</v>
-      </c>
-      <c r="L21" s="84">
-        <f>K13-J13</f>
-        <v>-2.5000000000000092E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E22" s="85"/>
-      <c r="F22" s="88"/>
-      <c r="J22" s="65"/>
-      <c r="K22" t="s">
-        <v>104</v>
-      </c>
-      <c r="L22" s="125">
-        <f>-L20/(J17*L21)</f>
-        <v>6.9499968171497342</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="I24" s="136" t="s">
-        <v>152</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274186D6-0845-4086-8645-5129374C9F00}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="126"/>
-      <c r="D11" s="126" t="s">
-        <v>296</v>
-      </c>
-      <c r="E11" s="126" t="s">
-        <v>310</v>
-      </c>
-      <c r="F11" s="242" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="240">
-        <v>0.04</v>
-      </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="240">
-        <f>C12+D12</f>
-        <v>0.04</v>
-      </c>
-      <c r="F12" s="240">
-        <f>E12</f>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>293</v>
-      </c>
-      <c r="C13" s="240"/>
-      <c r="D13" s="240">
-        <v>0.02</v>
-      </c>
-      <c r="E13" s="240">
-        <f>C12+D13</f>
-        <v>0.06</v>
-      </c>
-      <c r="F13" s="240">
-        <f>E13</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="240"/>
-      <c r="D14" s="240">
-        <v>0.01</v>
-      </c>
-      <c r="E14" s="240">
-        <f>C12+D14</f>
-        <v>0.05</v>
-      </c>
-      <c r="F14" s="241">
-        <f>E14/(1-B9)</f>
-        <v>7.8125E-2</v>
-      </c>
-      <c r="G14" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(F14)</f>
-        <v>=E14/(1-B9)</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A65F9133-00E1-449E-9ADA-4CB5979256BB}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -3248,37 +2558,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="94"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96"/>
+      <c r="A1" s="90"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="92"/>
       <c r="L1" t="s">
-        <v>115</v>
-      </c>
-      <c r="M1" s="89"/>
+        <v>105</v>
+      </c>
+      <c r="M1" s="85"/>
       <c r="Q1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="R1" t="s">
-        <v>116</v>
-      </c>
-      <c r="S1" s="138" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="S1" s="121" t="s">
+        <v>107</v>
       </c>
       <c r="X1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Y1" s="12">
         <v>2.8</v>
       </c>
       <c r="AA1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB1">
         <v>0</v>
@@ -3288,36 +2598,36 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97" t="str">
+      <c r="A2" s="93" t="str">
         <f>"Suppose that a firm’s recent earnings per share and dividend per share are "&amp;TEXT(N2,"$0.00")&amp;" and "&amp;(TEXT(N3,"$0.00")&amp;", respectively")</f>
         <v>Suppose that a firm’s recent earnings per share and dividend per share are $2.00 and $1.00, respectively</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="94"/>
       <c r="M2" s="13" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="N2" s="83">
         <v>2</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q2" s="18">
         <v>0</v>
       </c>
-      <c r="R2" s="92">
+      <c r="R2" s="88">
         <f>N3</f>
         <v>1</v>
       </c>
-      <c r="S2" s="139"/>
+      <c r="S2" s="122"/>
       <c r="X2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Y2" s="12">
         <v>1.8</v>
       </c>
       <c r="AA2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB2">
         <v>1</v>
@@ -3332,19 +2642,19 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="str">
+      <c r="A3" s="93" t="str">
         <f>"The growth rate is expected to be "&amp;TEXT(N4,"0.00%")&amp; " going forward."</f>
         <v>The growth rate is expected to be 15.00% going forward.</v>
       </c>
-      <c r="J3" s="98"/>
+      <c r="J3" s="94"/>
       <c r="M3" s="13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="N3" s="83">
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -3353,18 +2663,18 @@
         <f>R2*(1+$N$4)</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="S3" s="140">
+      <c r="S3" s="123">
         <f t="shared" ref="S3:S8" si="1">R3/(1+$N$7)^Q3</f>
         <v>1</v>
       </c>
       <c r="X3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Y3" s="63">
         <v>0.08</v>
       </c>
       <c r="AA3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB3">
         <v>2</v>
@@ -3379,19 +2689,19 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="str">
+      <c r="A4" s="93" t="str">
         <f>"However, the firm’s current P/E ratio of " &amp; TEXT(N5,"0") &amp; " seems high for this growth rate. The P/E ratio is expected to fall to " &amp; TEXT(N6,"0") &amp; " within five years."</f>
         <v>However, the firm’s current P/E ratio of 25 seems high for this growth rate. The P/E ratio is expected to fall to 20 within five years.</v>
       </c>
-      <c r="J4" s="98"/>
+      <c r="J4" s="94"/>
       <c r="M4" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="N4" s="90">
+        <v>110</v>
+      </c>
+      <c r="N4" s="86">
         <v>0.15</v>
       </c>
       <c r="P4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -3400,18 +2710,18 @@
         <f>R3*(1+$N$4)</f>
         <v>1.3224999999999998</v>
       </c>
-      <c r="S4" s="140">
+      <c r="S4" s="123">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="Y4">
         <v>27</v>
       </c>
       <c r="AA4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB4">
         <v>3</v>
@@ -3426,16 +2736,16 @@
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="97"/>
-      <c r="J5" s="98"/>
+      <c r="A5" s="93"/>
+      <c r="J5" s="94"/>
       <c r="M5" s="13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="N5">
         <v>25</v>
       </c>
       <c r="P5" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -3444,18 +2754,18 @@
         <f>R4*(1+$N$4)</f>
         <v>1.5208749999999995</v>
       </c>
-      <c r="S5" s="140">
+      <c r="S5" s="123">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="Y5">
         <v>23</v>
       </c>
       <c r="AA5" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB5">
         <v>4</v>
@@ -3470,18 +2780,18 @@
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="97" t="s">
-        <v>129</v>
-      </c>
-      <c r="J6" s="98"/>
+      <c r="A6" s="93" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="94"/>
       <c r="M6" s="13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -3490,18 +2800,18 @@
         <f>R5*(1+$N$4)</f>
         <v>1.7490062499999994</v>
       </c>
-      <c r="S6" s="140">
+      <c r="S6" s="123">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="Y6" s="1">
         <v>0.1</v>
       </c>
       <c r="AA6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -3516,18 +2826,18 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="97" t="s">
-        <v>130</v>
-      </c>
-      <c r="J7" s="98"/>
+      <c r="A7" s="93" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" s="94"/>
       <c r="M7" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="N7" s="91">
+        <v>114</v>
+      </c>
+      <c r="N7" s="87">
         <v>0.15</v>
       </c>
       <c r="P7" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3536,7 +2846,7 @@
         <f>R6*(1+$N$4)</f>
         <v>2.0113571874999994</v>
       </c>
-      <c r="S7" s="140">
+      <c r="S7" s="123">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3546,40 +2856,40 @@
       <c r="AB7" s="18">
         <v>5</v>
       </c>
-      <c r="AC7" s="92">
+      <c r="AC7" s="88">
         <f>Y10</f>
         <v>94.624728145920017</v>
       </c>
-      <c r="AD7" s="92">
+      <c r="AD7" s="88">
         <f t="shared" si="0"/>
         <v>47.045213418076713</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99" t="str">
+      <c r="A8" s="95" t="str">
         <f>"Calculate the present value of these cash flows using a " &amp; TEXT(N7,"0.00%") &amp;" percent discount rate."</f>
         <v>Calculate the present value of these cash flows using a 15.00% percent discount rate.</v>
       </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="101"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="97"/>
       <c r="P8" s="18" t="s">
         <v>12</v>
       </c>
       <c r="Q8" s="18">
         <v>5</v>
       </c>
-      <c r="R8" s="137">
+      <c r="R8" s="120">
         <f>N11</f>
         <v>80.454287499999978</v>
       </c>
-      <c r="S8" s="141">
+      <c r="S8" s="124">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -3589,10 +2899,10 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="R9" s="138" t="s">
-        <v>125</v>
-      </c>
-      <c r="S9" s="140">
+      <c r="R9" s="121" t="s">
+        <v>115</v>
+      </c>
+      <c r="S9" s="123">
         <f>SUM(S3:S8)</f>
         <v>45</v>
       </c>
@@ -3601,18 +2911,18 @@
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="N10" s="12"/>
       <c r="X10" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="Y10" s="12">
         <f>Y5*(Y1*(1+Y3)^AB7)</f>
         <v>94.624728145920017</v>
       </c>
-      <c r="AB10" s="93"/>
+      <c r="AB10" s="89"/>
       <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="M11" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N11" s="69">
         <f>N6*(N2*(1+N4)^Q8)</f>
@@ -3623,21 +2933,21 @@
         <v>=N6*(N2*(1+N4)^Q8)</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="S11" s="69">
         <f>NPV(N7,R3,R4,R5,R6,R7+R8)</f>
         <v>45</v>
       </c>
       <c r="X11" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB11" s="93"/>
+        <v>118</v>
+      </c>
+      <c r="AB11" s="89"/>
       <c r="AC11" s="12"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="M12" s="86" t="s">
-        <v>128</v>
+      <c r="M12" s="84" t="s">
+        <v>118</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -3650,7 +2960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6771D98C-B68B-4928-87E0-6C7B1111504C}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -3679,104 +2989,104 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="D1" s="64"/>
       <c r="G1" s="64"/>
       <c r="H1" s="64"/>
       <c r="N1"/>
-      <c r="O1" s="177" t="s">
-        <v>217</v>
-      </c>
-      <c r="P1" s="178">
+      <c r="O1" s="160" t="s">
+        <v>197</v>
+      </c>
+      <c r="P1" s="161">
         <v>30000</v>
       </c>
       <c r="Q1"/>
       <c r="R1"/>
     </row>
     <row r="2" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="179" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="180" t="s">
+      <c r="A2" s="162" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="181" t="s">
-        <v>219</v>
-      </c>
-      <c r="D2" s="182" t="s">
-        <v>220</v>
-      </c>
-      <c r="E2" s="183" t="s">
-        <v>221</v>
-      </c>
-      <c r="F2" s="183" t="s">
-        <v>222</v>
-      </c>
-      <c r="G2" s="184" t="s">
-        <v>223</v>
-      </c>
-      <c r="H2" s="184" t="s">
-        <v>224</v>
-      </c>
-      <c r="I2" s="184" t="s">
-        <v>225</v>
-      </c>
-      <c r="J2" s="184" t="s">
-        <v>226</v>
-      </c>
-      <c r="K2" s="184" t="s">
-        <v>227</v>
-      </c>
-      <c r="L2" s="184" t="s">
-        <v>228</v>
-      </c>
-      <c r="M2" s="184" t="s">
-        <v>229</v>
+      <c r="C2" s="164" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="165" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="166" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="166" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="167" t="s">
+        <v>203</v>
+      </c>
+      <c r="H2" s="167" t="s">
+        <v>204</v>
+      </c>
+      <c r="I2" s="167" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="167" t="s">
+        <v>206</v>
+      </c>
+      <c r="K2" s="167" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" s="167" t="s">
+        <v>208</v>
+      </c>
+      <c r="M2" s="167" t="s">
+        <v>209</v>
       </c>
       <c r="N2"/>
-      <c r="O2" s="185" t="s">
-        <v>230</v>
-      </c>
-      <c r="P2" s="186">
+      <c r="O2" s="168" t="s">
+        <v>210</v>
+      </c>
+      <c r="P2" s="169">
         <v>1.6</v>
       </c>
       <c r="Q2"/>
       <c r="R2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="187" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" s="188">
+      <c r="A3" s="170" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="171">
         <f>P3</f>
         <v>2</v>
       </c>
-      <c r="C3" s="237">
+      <c r="C3" s="220">
         <v>16</v>
       </c>
-      <c r="D3" s="189">
+      <c r="D3" s="172">
         <f>ROUNDDOWN(E3/C3,0)</f>
         <v>875</v>
       </c>
-      <c r="E3" s="190">
+      <c r="E3" s="173">
         <f>F3*E5</f>
         <v>14000.000000000004</v>
       </c>
-      <c r="F3" s="245">
+      <c r="F3" s="226">
         <f>P5</f>
         <v>0.46666666666666679</v>
       </c>
-      <c r="G3" s="191">
+      <c r="G3" s="174">
         <f>(E3/$E$5)*B3</f>
         <v>0.93333333333333357</v>
       </c>
-      <c r="H3" s="192">
+      <c r="H3" s="175">
         <f>$B$8+B3*($B$7-$B$8)</f>
         <v>0.21</v>
       </c>
-      <c r="I3" s="193"/>
-      <c r="J3" s="194">
+      <c r="I3" s="176"/>
+      <c r="J3" s="177">
         <f>C3*(1+H3)-I3</f>
         <v>19.36</v>
       </c>
@@ -3792,90 +3102,90 @@
         <v>1.1239669421487601</v>
       </c>
       <c r="N3"/>
-      <c r="O3" s="177" t="s">
-        <v>232</v>
-      </c>
-      <c r="P3" s="195">
+      <c r="O3" s="160" t="s">
+        <v>212</v>
+      </c>
+      <c r="P3" s="178">
         <v>2</v>
       </c>
       <c r="Q3"/>
       <c r="R3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="196" t="s">
-        <v>233</v>
-      </c>
-      <c r="B4" s="197">
+      <c r="A4" s="179" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="180">
         <f>P4</f>
         <v>1.25</v>
       </c>
-      <c r="C4" s="238">
+      <c r="C4" s="221">
         <v>25</v>
       </c>
-      <c r="D4" s="189">
+      <c r="D4" s="172">
         <f>ROUNDDOWN(E4/C4,0)</f>
         <v>640</v>
       </c>
-      <c r="E4" s="198">
+      <c r="E4" s="181">
         <f>F4*E5</f>
         <v>15999.999999999996</v>
       </c>
-      <c r="F4" s="246">
+      <c r="F4" s="227">
         <f>P6</f>
         <v>0.53333333333333321</v>
       </c>
-      <c r="G4" s="199">
+      <c r="G4" s="182">
         <f>(E4/$E$5)*B4</f>
         <v>0.66666666666666652</v>
       </c>
-      <c r="H4" s="200">
+      <c r="H4" s="183">
         <f>$B$8+B4*($B$7-$B$8)</f>
         <v>0.14249999999999999</v>
       </c>
-      <c r="I4" s="236">
+      <c r="I4" s="219">
         <v>1</v>
       </c>
-      <c r="J4" s="201">
+      <c r="J4" s="184">
         <f>C4*(1+H4)-I4</f>
         <v>27.5625</v>
       </c>
       <c r="N4"/>
-      <c r="O4" s="185" t="s">
-        <v>234</v>
-      </c>
-      <c r="P4" s="202">
+      <c r="O4" s="168" t="s">
+        <v>214</v>
+      </c>
+      <c r="P4" s="185">
         <v>1.25</v>
       </c>
       <c r="Q4"/>
       <c r="R4"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="203" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="193"/>
-      <c r="C5" s="193"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="204">
+      <c r="A5" s="186" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="187">
         <f>P1</f>
         <v>30000</v>
       </c>
-      <c r="F5" s="205"/>
-      <c r="G5" s="206">
+      <c r="F5" s="188"/>
+      <c r="G5" s="189">
         <f>SUM(G3:G4)</f>
         <v>1.6</v>
       </c>
-      <c r="H5" s="207">
+      <c r="H5" s="190">
         <f>SUMPRODUCT(F3:F4,H3:H4)</f>
         <v>0.17399999999999999</v>
       </c>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
       <c r="N5"/>
-      <c r="O5" s="208" t="s">
-        <v>236</v>
-      </c>
-      <c r="P5" s="243">
+      <c r="O5" s="191" t="s">
+        <v>216</v>
+      </c>
+      <c r="P5" s="224">
         <f>(P2-P4)/(P3-P4)</f>
         <v>0.46666666666666679</v>
       </c>
@@ -3886,17 +3196,17 @@
       <c r="D6" s="64"/>
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
-      <c r="J6" s="247" t="s">
-        <v>237</v>
-      </c>
-      <c r="L6" s="209" t="s">
-        <v>238</v>
+      <c r="J6" s="228" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" s="192" t="s">
+        <v>218</v>
       </c>
       <c r="N6"/>
-      <c r="O6" s="210" t="s">
-        <v>239</v>
-      </c>
-      <c r="P6" s="244">
+      <c r="O6" s="193" t="s">
+        <v>219</v>
+      </c>
+      <c r="P6" s="225">
         <f>1-P5</f>
         <v>0.53333333333333321</v>
       </c>
@@ -3904,8 +3214,8 @@
       <c r="R6"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="203" t="s">
-        <v>240</v>
+      <c r="A7" s="186" t="s">
+        <v>220</v>
       </c>
       <c r="B7" s="2">
         <v>0.12</v>
@@ -3918,8 +3228,8 @@
       <c r="R7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="203" t="s">
-        <v>241</v>
+      <c r="A8" s="186" t="s">
+        <v>221</v>
       </c>
       <c r="B8" s="2">
         <v>0.03</v>
@@ -3940,206 +3250,206 @@
       <c r="R9"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="102" t="str">
+      <c r="A11" s="98" t="str">
         <f>"You have  " &amp; TEXT(E5,"$0,000") &amp; " to invest in Security A and Security B."</f>
         <v>You have  $30,000 to invest in Security A and Security B.</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="102" t="str">
+      <c r="A12" s="98" t="str">
         <f>"Security A has a beta of " &amp; TEXT(B3,"0.00") &amp; " and a price of " &amp; TEXT(C3,"$0")</f>
         <v>Security A has a beta of 2.00 and a price of $16</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="102" t="str">
+      <c r="A13" s="98" t="str">
         <f>"Security B has a beta of " &amp; TEXT(B4,"0.00") &amp; " and a price of " &amp; TEXT(C4,"$0")</f>
         <v>Security B has a beta of 1.25 and a price of $25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="102" t="str">
+      <c r="A14" s="98" t="str">
         <f>"The risk free rate is  " &amp; TEXT(B8,"0.00%") &amp; "  and the expected return of the market is "  &amp; TEXT(B7,"0.00%")</f>
         <v>The risk free rate is  3.00%  and the expected return of the market is 12.00%</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="102" t="str">
+      <c r="A16" s="98" t="str">
         <f>"1. How many shares should you purchase of each to achieve a portfolio beta of "&amp; TEXT(G5,"0.00")&amp;"?"</f>
         <v>1. How many shares should you purchase of each to achieve a portfolio beta of 1.60?</v>
       </c>
-      <c r="B16" s="102"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="102"/>
+      <c r="A17" s="98"/>
       <c r="B17" t="s">
-        <v>242</v>
-      </c>
-      <c r="C17" s="211">
+        <v>222</v>
+      </c>
+      <c r="C17" s="194">
         <f>D3</f>
         <v>875</v>
       </c>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="102"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="102"/>
+      <c r="A18" s="98"/>
       <c r="B18" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" s="102">
+        <v>223</v>
+      </c>
+      <c r="C18" s="98">
         <f>D4</f>
         <v>640</v>
       </c>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="102" t="str">
+      <c r="A19" s="98" t="str">
         <f>"2. What is the expected return on Security A?"</f>
         <v>2. What is the expected return on Security A?</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="102"/>
+      <c r="A20" s="98"/>
       <c r="B20" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="212">
+        <v>224</v>
+      </c>
+      <c r="C20" s="195">
         <f>H3</f>
         <v>0.21</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="102"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="102" t="str">
+      <c r="A21" s="98" t="str">
         <f>"3. What is the expected return on Security B?"</f>
         <v>3. What is the expected return on Security B?</v>
       </c>
-      <c r="B21" s="102"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="102"/>
+      <c r="A22" s="98"/>
       <c r="B22" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="212">
+        <v>225</v>
+      </c>
+      <c r="C22" s="195">
         <f>H4</f>
         <v>0.14249999999999999</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="102"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="102" t="str">
+      <c r="A24" s="98" t="str">
         <f>"4. If Company B pays an end-of-year dividend of "&amp; TEXT(I4,"$0.00")&amp;".  What would the fair price of security B be in one year?"</f>
         <v>4. If Company B pays an end-of-year dividend of $1.00.  What would the fair price of security B be in one year?</v>
       </c>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="102"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="102"/>
+      <c r="A25" s="98"/>
       <c r="B25" t="s">
-        <v>246</v>
-      </c>
-      <c r="C25" s="213">
+        <v>226</v>
+      </c>
+      <c r="C25" s="196">
         <f>J4</f>
         <v>27.5625</v>
       </c>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="102" t="str">
+      <c r="A26" s="98" t="str">
         <f>"5. Security A does not pay a dividend. What do you think the the fair price of security A should be in one year (P1)?"</f>
         <v>5. Security A does not pay a dividend. What do you think the the fair price of security A should be in one year (P1)?</v>
       </c>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="102"/>
+      <c r="A27" s="98"/>
       <c r="B27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C27" s="213">
+        <v>227</v>
+      </c>
+      <c r="C27" s="196">
         <f>J3</f>
         <v>19.36</v>
       </c>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="102"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="102" t="str">
+      <c r="A29" s="98" t="str">
         <f>"6. An equity research analyst thinks Security A expected price in 1-year (P1) is " &amp;TEXT(K3,"$0.00") &amp; ".  "</f>
         <v xml:space="preserve">6. An equity research analyst thinks Security A expected price in 1-year (P1) is $18.00.  </v>
       </c>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="102"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="102" t="str">
+      <c r="A30" s="98" t="str">
         <f>"         Given that data, what would be the current intrinsic value (P0) for security A ? Is the stock over or under valued compared to the price per share?"</f>
         <v xml:space="preserve">         Given that data, what would be the current intrinsic value (P0) for security A ? Is the stock over or under valued compared to the price per share?</v>
       </c>
-      <c r="B30" s="102"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="102"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="C31" s="12">
         <f>L3</f>
@@ -4148,7 +3458,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="C32" t="str">
         <f>IF(M3&gt;0,"Over","Under")</f>
@@ -4157,7 +3467,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C33" s="12">
         <f>M3</f>
@@ -4166,7 +3476,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +3484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DD48E3-D2F2-4CA7-B20E-1A62138DDEA3}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -4190,34 +3500,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
-        <v>252</v>
+      <c r="A1" s="99" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="214" t="s">
-        <v>253</v>
-      </c>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="214"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="215"/>
+      <c r="B4" s="197"/>
+      <c r="C4" s="197"/>
+      <c r="D4" s="197" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
+      <c r="G4" s="197"/>
+      <c r="H4" s="197"/>
+      <c r="I4" s="198"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="216" t="s">
-        <v>254</v>
+      <c r="A5" s="199" t="s">
+        <v>234</v>
       </c>
       <c r="B5" s="83">
         <v>0.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="126">
+        <v>235</v>
+      </c>
+      <c r="E5" s="119">
         <v>0</v>
       </c>
       <c r="F5" s="18">
@@ -4229,106 +3539,106 @@
       <c r="H5" s="18">
         <v>3</v>
       </c>
-      <c r="I5" s="217" t="s">
-        <v>256</v>
+      <c r="I5" s="200" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" s="91">
+        <v>237</v>
+      </c>
+      <c r="B6" s="87">
         <v>0.18</v>
       </c>
       <c r="D6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E6" s="218"/>
-      <c r="F6" s="194">
+        <v>238</v>
+      </c>
+      <c r="E6" s="201"/>
+      <c r="F6" s="177">
         <f>$B$5*(1+$B$6)^F5</f>
         <v>0.59</v>
       </c>
-      <c r="G6" s="194">
+      <c r="G6" s="177">
         <f>$B$5*(1+$B$6)^G5</f>
         <v>0.69619999999999993</v>
       </c>
-      <c r="H6" s="194">
+      <c r="H6" s="177">
         <f>$B$5*(1+$B$6)^H5</f>
         <v>0.82151599999999991</v>
       </c>
-      <c r="I6" s="219"/>
+      <c r="I6" s="202"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="90">
+        <v>239</v>
+      </c>
+      <c r="B7" s="86">
         <v>0.1</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="191"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="I7" s="194">
+        <v>240</v>
+      </c>
+      <c r="E7" s="174"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="I7" s="177">
         <f>H6*(1+B7)/(B8-B7)</f>
         <v>45.183380000000021</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="91">
+        <v>114</v>
+      </c>
+      <c r="B8" s="87">
         <v>0.12</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
-      </c>
-      <c r="E8" s="220">
+        <v>241</v>
+      </c>
+      <c r="E8" s="203">
         <f>NPV(B8,F6,G6,H6+I7)</f>
         <v>33.827168367346943</v>
       </c>
-      <c r="F8" s="193"/>
-      <c r="G8" s="193"/>
-      <c r="H8" s="193"/>
-      <c r="I8" s="193"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="104">
+        <v>242</v>
+      </c>
+      <c r="B9" s="100">
         <v>3</v>
       </c>
       <c r="E9" s="64"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
-      <c r="D10" s="214" t="s">
-        <v>263</v>
-      </c>
-      <c r="E10" s="221"/>
-      <c r="F10" s="214"/>
-      <c r="G10" s="214"/>
-      <c r="H10" s="214"/>
-      <c r="I10" s="215"/>
+      <c r="B10" s="197"/>
+      <c r="C10" s="197"/>
+      <c r="D10" s="197" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" s="204"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="197"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="198"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="216" t="s">
-        <v>254</v>
+      <c r="A11" s="199" t="s">
+        <v>234</v>
       </c>
       <c r="B11" s="12">
         <f>B5</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="E11" s="126">
+        <v>235</v>
+      </c>
+      <c r="E11" s="119">
         <v>0</v>
       </c>
       <c r="F11" s="18">
@@ -4340,20 +3650,20 @@
       <c r="H11" s="18">
         <v>3</v>
       </c>
-      <c r="I11" s="222" t="s">
-        <v>256</v>
+      <c r="I11" s="205" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="216" t="s">
-        <v>257</v>
+      <c r="A12" s="199" t="s">
+        <v>237</v>
       </c>
       <c r="B12" s="1">
         <f>B6</f>
         <v>0.18</v>
       </c>
       <c r="D12" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="E12" s="65"/>
       <c r="F12" s="12">
@@ -4371,25 +3681,25 @@
       <c r="I12" s="58"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" s="223">
+      <c r="A13" s="199" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="206">
         <f>B7</f>
         <v>0.1</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E13" s="64"/>
-      <c r="I13" s="224">
+      <c r="I13" s="207">
         <f>(H12*(1+B13))/(B14-B13)</f>
         <v>45.183380000000021</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="216" t="s">
-        <v>124</v>
+      <c r="A14" s="199" t="s">
+        <v>114</v>
       </c>
       <c r="B14" s="1">
         <f>B8</f>
@@ -4398,37 +3708,37 @@
       <c r="D14" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="225"/>
-      <c r="F14" s="226">
+      <c r="E14" s="208"/>
+      <c r="F14" s="209">
         <f>F12/((1+$B$8)^F5)</f>
         <v>0.52678571428571419</v>
       </c>
-      <c r="G14" s="226">
+      <c r="G14" s="209">
         <f>G12/((1+$B$8)^G5)</f>
         <v>0.55500637755102022</v>
       </c>
-      <c r="H14" s="226">
+      <c r="H14" s="209">
         <f>H12/((1+$B$8)^H5)</f>
         <v>0.584738862062682</v>
       </c>
-      <c r="I14" s="227">
+      <c r="I14" s="210">
         <f>I13/((1+$B$8)^H11)</f>
         <v>32.160637413447525</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="228">
+        <v>242</v>
+      </c>
+      <c r="B15" s="211">
         <f>B9</f>
         <v>3</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="229">
+        <v>241</v>
+      </c>
+      <c r="E15" s="212">
         <f>SUM(F14:I14)</f>
         <v>33.827168367346943</v>
       </c>
@@ -4499,7 +3809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AC71B9-F875-4331-AD1C-C4F77D609F2B}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -4514,81 +3824,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
-        <v>131</v>
+      <c r="A1" s="99" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="str">
+      <c r="A3" s="101" t="str">
         <f>"A firm does not pay a dividend. It is expected to pay its first dividend of " &amp; TEXT(B10,"$0.00")&amp; " per share in "&amp; TEXT(B9,"0")&amp;" years. This dividend will grow at " &amp; TEXT(B7,"0.00%") &amp;" percent indefinitely."</f>
         <v>A firm does not pay a dividend. It is expected to pay its first dividend of $2.00 per share in 3 years. This dividend will grow at 8.00% percent indefinitely.</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="107"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="108" t="str">
+      <c r="A4" s="104" t="str">
         <f>" Use a " &amp;TEXT(B8,"0.00%")&amp;" percent discount rate."</f>
         <v xml:space="preserve"> Use a 15.00% percent discount rate.</v>
       </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="109"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="105"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="110" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="112"/>
+      <c r="A5" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="108"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="91">
+        <v>110</v>
+      </c>
+      <c r="B7" s="87">
         <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="91">
+        <v>123</v>
+      </c>
+      <c r="B8" s="87">
         <v>0.15</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="104">
+        <v>132</v>
+      </c>
+      <c r="B9" s="100">
         <v>3</v>
       </c>
     </row>
@@ -4604,9 +3914,9 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="104">
+        <v>124</v>
+      </c>
+      <c r="B11" s="100">
         <f>B9-1</f>
         <v>2</v>
       </c>
@@ -4617,7 +3927,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B13" s="12">
         <f>B10/(B8-B7)</f>
@@ -4630,7 +3940,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B14" s="12">
         <f>B13/(1+B8)^B11</f>
@@ -4646,7 +3956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B053C31B-F6B7-4D1D-8C6B-72374219DA74}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -4660,7 +3970,7 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B3" s="10">
         <v>15000</v>
@@ -4671,26 +3981,26 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="B6" s="12">
         <v>42.88</v>
       </c>
-      <c r="C6" s="240">
+      <c r="C6" s="223">
         <v>0.3</v>
       </c>
       <c r="D6" s="10">
@@ -4708,12 +4018,12 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="B7" s="12">
         <v>51.32</v>
       </c>
-      <c r="C7" s="240">
+      <c r="C7" s="223">
         <v>0.4</v>
       </c>
       <c r="D7" s="10">
@@ -4731,12 +4041,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="B8" s="12">
         <v>8.51</v>
       </c>
-      <c r="C8" s="240">
+      <c r="C8" s="223">
         <v>0.3</v>
       </c>
       <c r="D8" s="10">
@@ -4757,7 +4067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748E5A36-5034-488B-AEF2-31F710CDEA28}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -4770,7 +4080,7 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>500</v>
@@ -4778,7 +4088,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="C3" s="12">
         <v>103.39</v>
@@ -4786,15 +4096,15 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="144">
+        <v>273</v>
+      </c>
+      <c r="C4" s="127">
         <v>0.35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="C5" s="12">
         <v>106.69</v>
@@ -4802,7 +4112,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="C7" s="12">
         <f>((C5-C3)+C4)*C2</f>
@@ -4811,7 +4121,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="C8" s="11">
         <f>C7/(C3*C2)</f>
@@ -4823,7 +4133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB18100-7802-47A4-927A-CF793B15C087}">
   <sheetPr>
     <tabColor rgb="FFEE0000"/>
@@ -4837,22 +4147,22 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B5" s="10">
         <v>30000</v>
@@ -4864,7 +4174,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="231" t="str">
+      <c r="A8" s="214" t="str">
         <f>TEXT(A3,"")&amp; " is considering buying "&amp;TEXT(A4,"")&amp;" that will generate perpetual after-tax cash flows of "&amp;TEXT(B27,"$0,000")&amp;" per year beginning next year."</f>
         <v>Big Firm is considering buying Small Firm that will generate perpetual after-tax cash flows of $30,000 per year beginning next year.</v>
       </c>
@@ -4888,38 +4198,38 @@
       <c r="S8" s="57"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="230" t="s">
-        <v>276</v>
+      <c r="A9" s="213" t="s">
+        <v>256</v>
       </c>
       <c r="S9" s="58"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="230" t="str">
+      <c r="A10" s="213" t="str">
         <f>"Cost of Equity including flotation costs is " &amp;TEXT( B21,"0.00%") &amp;" and debt issues cost "&amp;TEXT(B22,"0.00%") &amp;" on an after-tax basis."</f>
         <v>Cost of Equity including flotation costs is 15.00% and debt issues cost 5.00% on an after-tax basis.</v>
       </c>
       <c r="S10" s="58"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="230" t="str">
+      <c r="A11" s="213" t="str">
         <f>"The current capital structure is " &amp;TEXT(B16,"0.00%")&amp; " debt and "&amp;TEXT(B17,"0.00%") &amp;" equity."</f>
         <v>The current capital structure is 30.00% debt and 70.00% equity.</v>
       </c>
       <c r="S11" s="58"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="230"/>
+      <c r="A12" s="213"/>
       <c r="S12" s="58"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="230" t="s">
-        <v>277</v>
+      <c r="A13" s="213" t="s">
+        <v>257</v>
       </c>
       <c r="S13" s="58"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="230" t="s">
-        <v>278</v>
+      <c r="A14" s="213" t="s">
+        <v>258</v>
       </c>
       <c r="S14" s="58"/>
     </row>
@@ -4957,14 +4267,14 @@
       <c r="A17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="232">
+      <c r="B17" s="215">
         <v>0.7</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="B18" s="2">
         <f>B16+B17</f>
@@ -4973,7 +4283,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B21" s="2">
         <v>0.15</v>
@@ -4981,24 +4291,24 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B22" s="1">
         <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="233" t="s">
-        <v>282</v>
-      </c>
-      <c r="B24" s="234">
+      <c r="A24" s="216" t="s">
+        <v>262</v>
+      </c>
+      <c r="B24" s="217">
         <f>(B21*B17)+(B22*B16)</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B27" s="10">
         <v>30000</v>
@@ -5006,14 +4316,14 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="233" t="s">
-        <v>285</v>
-      </c>
-      <c r="B31" s="235">
+      <c r="A31" s="216" t="s">
+        <v>265</v>
+      </c>
+      <c r="B31" s="218">
         <f>B27/B24</f>
         <v>250000</v>
       </c>
@@ -5023,7 +4333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9458BEA2-912B-4733-9C99-A8EEABC3ED6D}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
@@ -5037,7 +4347,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5045,7 +4355,7 @@
         <v>63</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5053,11 +4363,11 @@
         <v>65</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="216"/>
+      <c r="A5" s="199"/>
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5067,19 +4377,19 @@
       <c r="B6" s="15"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="230" t="s">
-        <v>267</v>
+      <c r="A7" s="213" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="230" t="str">
+      <c r="A8" s="213" t="str">
         <f>"What is "&amp;TEXT(B3,"0.00%") &amp;" cost of equity using retained earnings?"</f>
         <v>What is IBM Corp cost of equity using retained earnings?</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B10" s="12">
         <v>50</v>
@@ -5103,7 +4413,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="B13" s="1">
         <v>0.05</v>
@@ -5111,7 +4421,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="B14" s="1">
         <v>0.15</v>
@@ -5119,7 +4429,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="B16" s="21">
         <f>B13+B12*(B14-B13)</f>
@@ -5127,90 +4437,90 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="248" t="s">
+      <c r="A24" s="229" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="57"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="249" t="s">
+      <c r="A25" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="250"/>
+      <c r="B25" s="231"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
-      <c r="B26" s="167"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="150"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="249" t="s">
+      <c r="A27" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="251">
+      <c r="B27" s="232">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="165" t="s">
+      <c r="A28" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="252"/>
+      <c r="B28" s="233"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="165" t="s">
+      <c r="A29" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="170">
+      <c r="B29" s="153">
         <v>0.06</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="165" t="s">
+      <c r="A30" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="170">
+      <c r="B30" s="153">
         <v>0.05</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="165" t="s">
+      <c r="A31" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="170">
+      <c r="B31" s="153">
         <v>0.15</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="165" t="s">
+      <c r="A32" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="167">
+      <c r="B32" s="150">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="216" t="s">
+      <c r="A33" s="199" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="253">
+      <c r="B33" s="234">
         <v>0.155</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="216"/>
+      <c r="A34" s="199"/>
       <c r="B34" s="58"/>
     </row>
     <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="254" t="s">
+      <c r="A35" s="235" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="222"/>
+      <c r="B35" s="205"/>
     </row>
     <row r="36" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="199" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="255">
+      <c r="B36" s="236">
         <f>B30+B32*(B31-B30)</f>
         <v>0.16499999999999998</v>
       </c>
@@ -5220,231 +4530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB5DD99-F9ED-426D-BBBC-222388BB61D8}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="113"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="115"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="116" t="str">
-        <f>"Create the amortization schedule for your new car loan of " &amp;TEXT(B7,"$0,000")&amp;", paid monthly over " &amp;TEXT(B9,"0")&amp; " years using an " &amp; TEXT(B8,"0.00%") &amp;" APR."</f>
-        <v>Create the amortization schedule for your new car loan of $25,000, paid monthly over 5 years using an 8.00% APR.</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="117"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="120"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="121">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="66">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="5">
-        <f>B9*B10</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="19">
-        <f>B8/B10</f>
-        <v>6.6666666666666671E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="12">
-        <f>PMT(B12,B11,B7)</f>
-        <v>-506.90985721034207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17" s="68">
-        <f>B7</f>
-        <v>25000</v>
-      </c>
-      <c r="C17" s="69">
-        <f>-$B$14</f>
-        <v>506.90985721034207</v>
-      </c>
-      <c r="D17" s="68">
-        <f>B17*B12</f>
-        <v>166.66666666666669</v>
-      </c>
-      <c r="E17" s="69">
-        <f>C17-D17</f>
-        <v>340.24319054367538</v>
-      </c>
-      <c r="F17" s="68">
-        <f>B17-E17</f>
-        <v>24659.756809456325</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" s="68">
-        <f>F17</f>
-        <v>24659.756809456325</v>
-      </c>
-      <c r="C18" s="12">
-        <f t="shared" ref="C18:C19" si="0">-$B$14</f>
-        <v>506.90985721034207</v>
-      </c>
-      <c r="D18" s="68">
-        <f t="shared" ref="D18:D19" si="1">B18*$B$8/12</f>
-        <v>164.39837872970884</v>
-      </c>
-      <c r="E18" s="69">
-        <f t="shared" ref="E18:E19" si="2">C18-D18</f>
-        <v>342.51147848063323</v>
-      </c>
-      <c r="F18" s="70">
-        <f t="shared" ref="F18:F19" si="3">B18-E18</f>
-        <v>24317.245330975693</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19" s="70">
-        <f>F18</f>
-        <v>24317.245330975693</v>
-      </c>
-      <c r="C19" s="12">
-        <f t="shared" si="0"/>
-        <v>506.90985721034207</v>
-      </c>
-      <c r="D19" s="68">
-        <f t="shared" si="1"/>
-        <v>162.11496887317131</v>
-      </c>
-      <c r="E19" s="69">
-        <f t="shared" si="2"/>
-        <v>344.79488833717073</v>
-      </c>
-      <c r="F19" s="70">
-        <f t="shared" si="3"/>
-        <v>23972.450442638521</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C25BF6-CC9C-4D8E-AB7A-1878F58DAAAE}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -5476,18 +4562,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="E2" s="248" t="s">
+      <c r="E2" s="229" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="57"/>
-      <c r="H2" s="248" t="s">
+      <c r="H2" s="229" t="s">
         <v>3</v>
       </c>
       <c r="I2" s="57"/>
-      <c r="K2" s="285" t="s">
+      <c r="K2" s="266" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="286"/>
+      <c r="L2" s="267"/>
       <c r="M2" s="56"/>
       <c r="N2" s="56"/>
       <c r="O2" s="57"/>
@@ -5504,24 +4590,24 @@
         <f t="shared" ref="C3:C9" ca="1" si="0">_xlfn.FORMULATEXT(B3)</f>
         <v>=F17</v>
       </c>
-      <c r="E3" s="249" t="s">
+      <c r="E3" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="250">
+      <c r="F3" s="231">
         <v>550000</v>
       </c>
       <c r="G3" s="13"/>
-      <c r="H3" s="249" t="s">
+      <c r="H3" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="262">
+      <c r="I3" s="243">
         <v>100000</v>
       </c>
       <c r="J3" s="13"/>
-      <c r="K3" s="267" t="s">
+      <c r="K3" s="248" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="268">
+      <c r="L3" s="249">
         <v>21000000</v>
       </c>
       <c r="O3" s="58"/>
@@ -5538,16 +4624,16 @@
         <f t="shared" ca="1" si="0"/>
         <v>=F28</v>
       </c>
-      <c r="E4" s="165"/>
-      <c r="F4" s="167"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="150"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="167"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="150"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="165" t="s">
+      <c r="K4" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="142">
+      <c r="L4" s="125">
         <v>1000</v>
       </c>
       <c r="O4" s="58"/>
@@ -5564,21 +4650,21 @@
         <f t="shared" ca="1" si="0"/>
         <v>=I14</v>
       </c>
-      <c r="E5" s="249" t="s">
+      <c r="E5" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="251">
+      <c r="F5" s="232">
         <v>45</v>
       </c>
       <c r="G5" s="13"/>
-      <c r="H5" s="249" t="s">
+      <c r="H5" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="251">
+      <c r="I5" s="232">
         <v>52</v>
       </c>
       <c r="J5" s="13"/>
-      <c r="K5" s="165" t="s">
+      <c r="K5" s="148" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="13">
@@ -5598,24 +4684,24 @@
         <f t="shared" ca="1" si="0"/>
         <v>=I22</v>
       </c>
-      <c r="E6" s="165" t="s">
+      <c r="E6" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="252">
+      <c r="F6" s="233">
         <v>3</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="165" t="s">
+      <c r="H6" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="252">
+      <c r="I6" s="233">
         <v>4</v>
       </c>
       <c r="J6" s="13"/>
-      <c r="K6" s="165" t="s">
+      <c r="K6" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="269">
+      <c r="L6" s="250">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="O6" s="58"/>
@@ -5632,21 +4718,21 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L14</v>
       </c>
-      <c r="E7" s="165" t="s">
+      <c r="E7" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="170">
+      <c r="F7" s="153">
         <v>0.06</v>
       </c>
       <c r="G7" s="13"/>
-      <c r="H7" s="165" t="s">
+      <c r="H7" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="263">
+      <c r="I7" s="244">
         <v>0.1</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="165" t="s">
+      <c r="K7" s="148" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="83">
@@ -5667,17 +4753,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L10</v>
       </c>
-      <c r="E8" s="165" t="s">
+      <c r="E8" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="170">
+      <c r="F8" s="153">
         <v>0.03</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="167"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="150"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="165" t="s">
+      <c r="K8" s="148" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="13">
@@ -5697,39 +4783,39 @@
         <f t="shared" ca="1" si="0"/>
         <v>=L17</v>
       </c>
-      <c r="E9" s="165" t="s">
+      <c r="E9" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="170">
+      <c r="F9" s="153">
         <v>0.1</v>
       </c>
       <c r="G9" s="13"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="167"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="150"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="249" t="s">
+      <c r="K9" s="230" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="270">
+      <c r="L9" s="251">
         <v>0.98499999999999999</v>
       </c>
       <c r="O9" s="58"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E10" s="165" t="s">
+      <c r="E10" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="167">
+      <c r="F10" s="150">
         <v>1.4</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="165"/>
-      <c r="I10" s="167"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="150"/>
       <c r="J10" s="13"/>
-      <c r="K10" s="165" t="s">
+      <c r="K10" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="269">
+      <c r="L10" s="250">
         <v>0.21</v>
       </c>
       <c r="O10" s="58"/>
@@ -5746,15 +4832,15 @@
         <f t="shared" ref="C11:C18" ca="1" si="1">_xlfn.FORMULATEXT(B11)</f>
         <v>=F3</v>
       </c>
-      <c r="E11" s="216" t="s">
+      <c r="E11" s="199" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="253">
+      <c r="F11" s="234">
         <v>0.2</v>
       </c>
-      <c r="H11" s="216"/>
+      <c r="H11" s="199"/>
       <c r="I11" s="58"/>
-      <c r="K11" s="216"/>
+      <c r="K11" s="199"/>
       <c r="O11" s="58"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -5769,11 +4855,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>=F5</v>
       </c>
-      <c r="E12" s="216"/>
+      <c r="E12" s="199"/>
       <c r="F12" s="58"/>
-      <c r="H12" s="216"/>
+      <c r="H12" s="199"/>
       <c r="I12" s="58"/>
-      <c r="K12" s="216" t="s">
+      <c r="K12" s="199" t="s">
         <v>28</v>
       </c>
       <c r="L12" s="12">
@@ -5794,15 +4880,15 @@
         <f t="shared" ca="1" si="1"/>
         <v>=I3</v>
       </c>
-      <c r="E13" s="254" t="s">
+      <c r="E13" s="235" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="222"/>
-      <c r="H13" s="254" t="s">
+      <c r="F13" s="205"/>
+      <c r="H13" s="235" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="58"/>
-      <c r="K13" s="216"/>
+      <c r="K13" s="199"/>
       <c r="L13" s="12"/>
       <c r="O13" s="58"/>
     </row>
@@ -5818,17 +4904,17 @@
         <f t="shared" ca="1" si="1"/>
         <v>=I5</v>
       </c>
-      <c r="E14" s="216" t="s">
+      <c r="E14" s="199" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="255">
+      <c r="F14" s="236">
         <f>F8+F10*(F9-F8)</f>
         <v>0.128</v>
       </c>
-      <c r="H14" s="264" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="243">
+      <c r="H14" s="245" t="s">
+        <v>134</v>
+      </c>
+      <c r="I14" s="224">
         <f>I6/I5</f>
         <v>7.6923076923076927E-2</v>
       </c>
@@ -5856,16 +4942,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L9</v>
       </c>
-      <c r="E15" s="216" t="s">
+      <c r="E15" s="199" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="255">
+      <c r="F15" s="236">
         <f>F6/F5+F7</f>
         <v>0.12666666666666665</v>
       </c>
-      <c r="H15" s="216"/>
+      <c r="H15" s="199"/>
       <c r="I15" s="58"/>
-      <c r="K15" s="216"/>
+      <c r="K15" s="199"/>
       <c r="M15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(L14)</f>
         <v>=L8*RATE(L5*L8,(-L7/L8),L12,-L4)</v>
@@ -5884,11 +4970,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L3</v>
       </c>
-      <c r="E16" s="216"/>
+      <c r="E16" s="199"/>
       <c r="F16" s="58"/>
-      <c r="H16" s="216"/>
+      <c r="H16" s="199"/>
       <c r="I16" s="58"/>
-      <c r="K16" s="216"/>
+      <c r="K16" s="199"/>
       <c r="O16" s="58"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -5903,19 +4989,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>=L4</v>
       </c>
-      <c r="E17" s="256" t="s">
+      <c r="E17" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="257">
+      <c r="F17" s="238">
         <f>AVERAGE(F14:F15)</f>
         <v>0.12733333333333333</v>
       </c>
-      <c r="H17" s="216"/>
+      <c r="H17" s="199"/>
       <c r="I17" s="58"/>
       <c r="K17" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="271">
+      <c r="L17" s="252">
         <f>L14*(1-L10)</f>
         <v>6.8261805524100397E-2</v>
       </c>
@@ -5936,20 +5022,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>=B15*B17</v>
       </c>
-      <c r="E18" s="216"/>
+      <c r="E18" s="199"/>
       <c r="F18" s="58"/>
-      <c r="H18" s="216"/>
+      <c r="H18" s="199"/>
       <c r="I18" s="58"/>
-      <c r="K18" s="216"/>
+      <c r="K18" s="199"/>
       <c r="O18" s="58"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" s="26"/>
-      <c r="E19" s="216"/>
+      <c r="E19" s="199"/>
       <c r="F19" s="58"/>
-      <c r="H19" s="216"/>
+      <c r="H19" s="199"/>
       <c r="I19" s="58"/>
-      <c r="K19" s="216"/>
+      <c r="K19" s="199"/>
       <c r="O19" s="58"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5957,15 +5043,15 @@
         <v>41</v>
       </c>
       <c r="B20" s="28"/>
-      <c r="E20" s="254" t="s">
+      <c r="E20" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="222"/>
-      <c r="H20" s="254" t="s">
+      <c r="F20" s="205"/>
+      <c r="H20" s="235" t="s">
         <v>43</v>
       </c>
       <c r="I20" s="58"/>
-      <c r="K20" s="216" t="s">
+      <c r="K20" s="199" t="s">
         <v>44</v>
       </c>
       <c r="O20" s="58"/>
@@ -5982,17 +5068,17 @@
         <f ca="1">_xlfn.FORMULATEXT(B21)</f>
         <v>=B11*B12</v>
       </c>
-      <c r="E21" s="216" t="s">
+      <c r="E21" s="199" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="258">
+      <c r="F21" s="239">
         <f>F5*F11</f>
         <v>9</v>
       </c>
-      <c r="H21" s="216" t="s">
+      <c r="H21" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="265">
+      <c r="I21" s="246">
         <f>I7*I5</f>
         <v>5.2</v>
       </c>
@@ -6016,17 +5102,17 @@
         <f ca="1">_xlfn.FORMULATEXT(B22)</f>
         <v>=B13*B14</v>
       </c>
-      <c r="E22" s="259" t="s">
+      <c r="E22" s="240" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="260">
+      <c r="F22" s="241">
         <f>F6/(F5-F21)+F7</f>
         <v>0.14333333333333331</v>
       </c>
-      <c r="H22" s="266" t="s">
+      <c r="H22" s="247" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="272">
+      <c r="I22" s="253">
         <f>I6/(I5-I21)</f>
         <v>8.5470085470085472E-2</v>
       </c>
@@ -6043,7 +5129,7 @@
         <f ca="1">_xlfn.FORMULATEXT(B23)</f>
         <v>=B16*B15</v>
       </c>
-      <c r="E23" s="216"/>
+      <c r="E23" s="199"/>
       <c r="F23" s="58"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -6054,17 +5140,17 @@
         <f>SUM(B21:B23)</f>
         <v>50635000</v>
       </c>
-      <c r="E24" s="216" t="s">
+      <c r="E24" s="199" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="255">
+      <c r="F24" s="236">
         <f>F22-F15</f>
         <v>1.6666666666666663E-2</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="33"/>
-      <c r="E25" s="216"/>
+      <c r="E25" s="199"/>
       <c r="F25" s="58"/>
     </row>
     <row r="26" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6072,10 +5158,10 @@
         <v>55</v>
       </c>
       <c r="B26" s="34"/>
-      <c r="E26" s="216" t="s">
+      <c r="E26" s="199" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="255">
+      <c r="F26" s="236">
         <f>F14+F24</f>
         <v>0.14466666666666667</v>
       </c>
@@ -6092,7 +5178,7 @@
         <f ca="1">_xlfn.FORMULATEXT(B27)</f>
         <v>=B21/$B$24</v>
       </c>
-      <c r="E27" s="216"/>
+      <c r="E27" s="199"/>
       <c r="F27" s="58"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -6107,10 +5193,10 @@
         <f ca="1">_xlfn.FORMULATEXT(B28)</f>
         <v>=B22/$B$24</v>
       </c>
-      <c r="E28" s="261" t="s">
+      <c r="E28" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="273">
+      <c r="F28" s="254">
         <f>AVERAGE(F26,F22)</f>
         <v>0.14399999999999999</v>
       </c>
@@ -6399,6 +5485,236 @@
   <mergeCells count="1">
     <mergeCell ref="K2:L2"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB5DD99-F9ED-426D-BBBC-222388BB61D8}">
+  <sheetPr>
+    <tabColor rgb="FF002060"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="61" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="111"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="112" t="str">
+        <f>"Create the amortization schedule for your new car loan of " &amp;TEXT(B7,"$0,000")&amp;", paid monthly over " &amp;TEXT(B9,"0")&amp; " years using an " &amp; TEXT(B8,"0.00%") &amp;" APR."</f>
+        <v>Create the amortization schedule for your new car loan of $25,000, paid monthly over 5 years using an 8.00% APR.</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="113"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="116"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="117">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="66">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="5">
+        <f>B9*B10</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="19">
+        <f>B8/B10</f>
+        <v>6.6666666666666671E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="12">
+        <f>PMT(B12,B11,B7)</f>
+        <v>-506.90985721034207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" s="68">
+        <f>B7</f>
+        <v>25000</v>
+      </c>
+      <c r="C17" s="69">
+        <f>-$B$14</f>
+        <v>506.90985721034207</v>
+      </c>
+      <c r="D17" s="68">
+        <f>B17*B12</f>
+        <v>166.66666666666669</v>
+      </c>
+      <c r="E17" s="69">
+        <f>C17-D17</f>
+        <v>340.24319054367538</v>
+      </c>
+      <c r="F17" s="68">
+        <f>B17-E17</f>
+        <v>24659.756809456325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="68">
+        <f>F17</f>
+        <v>24659.756809456325</v>
+      </c>
+      <c r="C18" s="12">
+        <f t="shared" ref="C18:C19" si="0">-$B$14</f>
+        <v>506.90985721034207</v>
+      </c>
+      <c r="D18" s="68">
+        <f t="shared" ref="D18:D19" si="1">B18*$B$8/12</f>
+        <v>164.39837872970884</v>
+      </c>
+      <c r="E18" s="69">
+        <f t="shared" ref="E18:E19" si="2">C18-D18</f>
+        <v>342.51147848063323</v>
+      </c>
+      <c r="F18" s="70">
+        <f t="shared" ref="F18:F19" si="3">B18-E18</f>
+        <v>24317.245330975693</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" s="70">
+        <f>F18</f>
+        <v>24317.245330975693</v>
+      </c>
+      <c r="C19" s="12">
+        <f t="shared" si="0"/>
+        <v>506.90985721034207</v>
+      </c>
+      <c r="D19" s="68">
+        <f t="shared" si="1"/>
+        <v>162.11496887317131</v>
+      </c>
+      <c r="E19" s="69">
+        <f t="shared" si="2"/>
+        <v>344.79488833717073</v>
+      </c>
+      <c r="F19" s="70">
+        <f t="shared" si="3"/>
+        <v>23972.450442638521</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="12"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6422,10 +5738,10 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="282"/>
-      <c r="F1" s="282"/>
+        <v>141</v>
+      </c>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
       <c r="G1" s="30"/>
       <c r="H1" s="30"/>
       <c r="I1" s="30"/>
@@ -6489,7 +5805,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B11">
         <v>25</v>
@@ -6499,23 +5815,23 @@
       <c r="A12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="144">
+      <c r="B12" s="127">
         <v>50000</v>
       </c>
-      <c r="C12" s="144"/>
+      <c r="C12" s="127"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="145">
+        <v>143</v>
+      </c>
+      <c r="B13" s="128">
         <v>475</v>
       </c>
-      <c r="C13" s="145"/>
+      <c r="C13" s="128"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B14">
         <f>65-B11</f>
@@ -6524,7 +5840,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B15" s="2">
         <v>7.0000000000000007E-2</v>
@@ -6541,7 +5857,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B17">
         <f>B14*B16</f>
@@ -6550,7 +5866,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B18" s="11">
         <f>B15/B16</f>
@@ -6560,7 +5876,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B20" s="12">
         <f>FV(B18,B17,-B13,-B12)</f>
@@ -6572,16 +5888,16 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="146" t="s">
-        <v>169</v>
+      <c r="B21" s="129" t="s">
+        <v>149</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="147">
+        <v>150</v>
+      </c>
+      <c r="B22" s="130">
         <f>FV(B18,B17,0,-B12)</f>
         <v>815570.57451389579</v>
       </c>
@@ -6592,9 +5908,9 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>171</v>
-      </c>
-      <c r="B23" s="147">
+        <v>151</v>
+      </c>
+      <c r="B23" s="130">
         <f>FV(B18,B17,-B13,0)</f>
         <v>1246786.3642083446</v>
       </c>
@@ -6605,9 +5921,9 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B24" s="147">
+        <v>152</v>
+      </c>
+      <c r="B24" s="130">
         <f>SUM(B22:B23)</f>
         <v>2062356.9387222403</v>
       </c>
@@ -6640,7 +5956,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6648,45 +5964,45 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B5" s="142">
+        <v>266</v>
+      </c>
+      <c r="B5" s="125">
         <v>5000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="142">
+        <v>104</v>
+      </c>
+      <c r="B6" s="125">
         <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B7" s="91">
+        <v>157</v>
+      </c>
+      <c r="B7" s="87">
         <v>0.09</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="239">
+        <v>267</v>
+      </c>
+      <c r="B9" s="222">
         <f xml:space="preserve"> NPER(B7,0,B5,-B6)</f>
         <v>8.0432317269320457</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B11">
         <f>72/9</f>
@@ -6711,23 +6027,23 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B3" s="275">
+        <v>283</v>
+      </c>
+      <c r="B3" s="256">
         <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B4" s="275">
+        <v>284</v>
+      </c>
+      <c r="B4" s="256">
         <v>150000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -6743,7 +6059,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="B7">
         <f>B5*B6</f>
@@ -6752,9 +6068,9 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="274">
+        <v>157</v>
+      </c>
+      <c r="B9" s="255">
         <f>RATE(B7,-B3,0,B4)*12</f>
         <v>1.3711616116975691E-2</v>
       </c>
@@ -6781,33 +6097,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="278" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="279"/>
-      <c r="C3" s="279"/>
-      <c r="D3" s="279"/>
-      <c r="E3" s="279"/>
+      <c r="A3" s="259" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="276">
+      <c r="B6" s="257">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="276">
+        <v>284</v>
+      </c>
+      <c r="B7" s="257">
         <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="B8" s="1">
         <v>0.09</v>
@@ -6815,9 +6131,9 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B10" s="277">
+        <v>288</v>
+      </c>
+      <c r="B10" s="258">
         <f>NPER(B8,0,B6,-B7)</f>
         <v>8.0432317269320457</v>
       </c>
@@ -6851,22 +6167,22 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="148" t="str">
+      <c r="A2" s="131" t="str">
         <f>"Calculate the dollar bond value of a zero-coupon bond that matures in "&amp;TEXT(B11,"")&amp; " years if the market interest rate is " &amp;TEXT(B10,"0.00%")</f>
         <v>Calculate the dollar bond value of a zero-coupon bond that matures in  years if the market interest rate is 7.50%</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="148" t="s">
-        <v>173</v>
+      <c r="A3" s="131" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="148"/>
+      <c r="A4" s="131"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12">
@@ -6876,7 +6192,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="2">
@@ -6886,7 +6202,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B8" s="10">
         <v>1000</v>
@@ -6902,7 +6218,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2">
         <v>7.4999999999999997E-2</v>
@@ -6943,10 +6259,10 @@
       </c>
     </row>
     <row r="21" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A21" s="148"/>
+      <c r="A21" s="131"/>
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="148"/>
+      <c r="A22" s="131"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6971,20 +6287,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="149"/>
-      <c r="B1" s="126" t="s">
+      <c r="A1" s="132"/>
+      <c r="B1" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126" t="s">
+      <c r="C1" s="119"/>
+      <c r="D1" s="119" t="s">
         <v>100</v>
       </c>
       <c r="I1" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="133" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="7">
@@ -6996,11 +6312,11 @@
         <v>14.5</v>
       </c>
       <c r="I2" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="133" t="s">
         <v>101</v>
       </c>
       <c r="B3" s="11">
@@ -7013,7 +6329,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -7022,12 +6338,12 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <f>B2*B4</f>
@@ -7040,7 +6356,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B6" s="11">
         <f>B3/B4</f>
@@ -7051,12 +6367,12 @@
         <v>0.03</v>
       </c>
       <c r="I6" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B7" s="12">
         <f>(B3*B9)/B4</f>
@@ -7067,12 +6383,12 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B9" s="10">
         <v>1000</v>
@@ -7081,7 +6397,7 @@
         <v>1000</v>
       </c>
       <c r="I9" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -7091,19 +6407,19 @@
       <c r="B10" s="83">
         <v>1000</v>
       </c>
-      <c r="D10" s="151">
+      <c r="D10" s="134">
         <f>PV(D13,D5,-D7,-D9)</f>
         <v>1102.267749537901</v>
       </c>
       <c r="I10" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="90">
+      <c r="B11" s="86">
         <f>B10/B9</f>
         <v>1</v>
       </c>
@@ -7112,17 +6428,17 @@
         <v>1.102267749537901</v>
       </c>
       <c r="I11" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="B13" s="2">
         <f>RATE(B5,-B6*B9,B10,-B9)</f>
@@ -7134,23 +6450,23 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
-        <v>183</v>
-      </c>
-      <c r="B14" s="153">
+      <c r="A14" s="135" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" s="136">
         <f>B13*B4</f>
         <v>6.0000000000001559E-2</v>
       </c>
-      <c r="D14" s="154">
+      <c r="D14" s="137">
         <v>0.05</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="149"/>
+      <c r="A15" s="132"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="149" t="s">
-        <v>184</v>
+      <c r="B16" s="132" t="s">
+        <v>164</v>
       </c>
       <c r="C16" s="12">
         <f>D10-B10</f>
@@ -7158,8 +6474,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="155" t="s">
-        <v>185</v>
+      <c r="B17" s="138" t="s">
+        <v>165</v>
       </c>
       <c r="C17" s="12">
         <f>D7</f>
@@ -7167,8 +6483,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="155" t="s">
-        <v>186</v>
+      <c r="B18" s="138" t="s">
+        <v>166</v>
       </c>
       <c r="C18" s="12">
         <f>C16+C17</f>
@@ -7176,8 +6492,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="155" t="s">
-        <v>187</v>
+      <c r="B19" s="138" t="s">
+        <v>167</v>
       </c>
       <c r="C19" s="11">
         <f>C18/B10</f>
@@ -7185,10 +6501,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="155"/>
+      <c r="A20" s="138"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="155"/>
+      <c r="A21" s="138"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="61" t="s">
@@ -7196,7 +6512,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="156" t="str">
+      <c r="A23" s="139" t="str">
         <f>"A " &amp; TEXT($B$2,"0")&amp;" year bond with semi-annual coupons payments, with a "&amp; TEXT($B$3,"0.00%") &amp; " coupon rate is valued at a bond $$ value "&amp; TEXT($B$10,"$0,000")</f>
         <v>A 15 year bond with semi-annual coupons payments, with a 6.00% coupon rate is valued at a bond $$ value $1,000</v>
       </c>
@@ -7205,17 +6521,17 @@
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="157" t="str">
+      <c r="A24" s="140" t="str">
         <f>"and a quoted bond prices of " &amp; TEXT(B11,"0.00%")</f>
         <v>and a quoted bond prices of 100.00%</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="157"/>
+      <c r="A25" s="140"/>
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="155" t="s">
-        <v>188</v>
+      <c r="A26" s="138" t="s">
+        <v>168</v>
       </c>
       <c r="B26" s="2">
         <f>B14</f>
@@ -7226,14 +6542,14 @@
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="158" t="str">
+      <c r="A28" s="141" t="str">
         <f>"After receiving the first coupon payment, you sell the bond at a yield of  " &amp; TEXT(D14,"0.00%") &amp;"."</f>
         <v>After receiving the first coupon payment, you sell the bond at a yield of  5.00%.</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="149" t="s">
-        <v>189</v>
+      <c r="A29" s="132" t="s">
+        <v>169</v>
       </c>
       <c r="B29" s="12">
         <f>D10</f>
@@ -7244,8 +6560,8 @@
       <c r="B30" s="12"/>
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="149" t="s">
-        <v>190</v>
+      <c r="A31" s="132" t="s">
+        <v>170</v>
       </c>
       <c r="B31" s="12">
         <f>C16</f>
@@ -7253,8 +6569,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="149" t="s">
-        <v>191</v>
+      <c r="A32" s="132" t="s">
+        <v>171</v>
       </c>
       <c r="B32" s="12">
         <f>C17</f>
@@ -7262,8 +6578,8 @@
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="149" t="s">
-        <v>192</v>
+      <c r="A33" s="132" t="s">
+        <v>172</v>
       </c>
       <c r="B33" s="12">
         <f>C18</f>
@@ -7271,8 +6587,8 @@
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="149" t="s">
-        <v>193</v>
+      <c r="A34" s="132" t="s">
+        <v>173</v>
       </c>
       <c r="B34" s="2">
         <f>C19</f>
@@ -7280,43 +6596,43 @@
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="149"/>
+      <c r="A35" s="132"/>
     </row>
     <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="149"/>
+      <c r="A36" s="132"/>
     </row>
     <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="155"/>
+      <c r="A37" s="138"/>
     </row>
     <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="155"/>
+      <c r="A38" s="138"/>
     </row>
     <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="155"/>
+      <c r="A39" s="138"/>
     </row>
     <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="155"/>
+      <c r="A40" s="138"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="159"/>
+      <c r="A41" s="142"/>
     </row>
     <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="155"/>
+      <c r="A42" s="138"/>
     </row>
     <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="160"/>
+      <c r="A43" s="143"/>
     </row>
     <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="149"/>
+      <c r="A44" s="132"/>
     </row>
     <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="149"/>
+      <c r="A45" s="132"/>
     </row>
     <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="155"/>
+      <c r="A46" s="138"/>
     </row>
     <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="155"/>
+      <c r="A47" s="138"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7338,141 +6654,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="284" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
+      <c r="A1" s="265" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
     </row>
     <row r="2" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="283" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="283"/>
-      <c r="C2" s="283"/>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
+      <c r="A2" s="264" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="283" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" s="283"/>
-      <c r="C3" s="283"/>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
+      <c r="A3" s="264" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="264"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="283" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="283"/>
-      <c r="C4" s="283"/>
-      <c r="D4" s="283"/>
-      <c r="E4" s="283"/>
-      <c r="F4" s="283"/>
-      <c r="G4" s="283"/>
+      <c r="A4" s="264" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="283" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="283"/>
-      <c r="C5" s="283"/>
-      <c r="D5" s="283"/>
-      <c r="E5" s="283"/>
-      <c r="F5" s="283"/>
-      <c r="G5" s="283"/>
+      <c r="A5" s="264" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="264"/>
+      <c r="C5" s="264"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="283" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="283"/>
-      <c r="E6" s="283"/>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
+      <c r="A6" s="264" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="264"/>
+      <c r="C6" s="264"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="161"/>
-      <c r="B7" s="161"/>
-      <c r="C7" s="161"/>
-      <c r="D7" s="161"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="161"/>
+      <c r="A7" s="144"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="162">
+        <v>180</v>
+      </c>
+      <c r="B8" s="145">
         <v>0.98450000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="163" t="s">
-        <v>201</v>
-      </c>
-      <c r="B9" s="164">
+      <c r="A9" s="146" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="147">
         <v>0.36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="165" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="166">
+      <c r="A10" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="149">
         <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="165" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="167">
+      <c r="A11" s="148" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="150">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="168" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="169">
+      <c r="A12" s="151" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="152">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="165" t="s">
+      <c r="A13" s="148" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="170">
+      <c r="B13" s="153">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="171" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14" s="172">
+      <c r="A14" s="154" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="155">
         <f>B13*B10</f>
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="B16" s="5">
         <f>B11*2</f>
@@ -7481,7 +6797,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="B17" s="5">
         <f>B12*2</f>
@@ -7490,16 +6806,16 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="173">
+        <v>187</v>
+      </c>
+      <c r="B18" s="156">
         <f>B14/2</f>
         <v>22.5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="B20" s="12">
         <f>B8*B10</f>
@@ -7508,7 +6824,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B21" s="12">
         <f>B14</f>
@@ -7517,7 +6833,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B22" s="12">
         <f>B21+B10</f>
@@ -7525,26 +6841,26 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
-        <v>211</v>
-      </c>
-      <c r="B24" s="174">
+      <c r="A24" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="157">
         <f>B14/B20</f>
         <v>4.5708481462671403E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" s="175">
+        <v>103</v>
+      </c>
+      <c r="B26" s="158">
         <f>RATE(B16,-B18,B20,-B10)</f>
         <v>2.3223120114168081E-2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="B27" s="66">
         <f>B26*2</f>
@@ -7553,16 +6869,16 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="175">
+        <v>193</v>
+      </c>
+      <c r="B29" s="158">
         <f>RATE(B17,-B18,B20,-B22)</f>
         <v>2.8257927444819992E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B30" s="66">
         <f>B29*2</f>
@@ -7570,10 +6886,10 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="B32" s="176">
+      <c r="A32" s="84" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="159">
         <f>B27/(1-B9)</f>
         <v>7.2572250356775253E-2</v>
       </c>

--- a/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
+++ b/Spring 2026 Final Practice Problems and Solutions - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/Documents/GitHub/BUS210---Final-Exam-Practice-Problems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E0160D-A0EB-4240-80F0-41C09842B861}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{6607535C-6484-46EF-B23C-6F2B2626DE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40B1AB6-6082-40A8-8469-70709AD4F2F0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="934" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TVM #1-15" sheetId="19" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="294">
   <si>
     <t>Beta</t>
   </si>
@@ -763,9 +763,6 @@
   </si>
   <si>
     <t>By what amount?</t>
-  </si>
-  <si>
-    <t>8 points awarded for everything right except #6</t>
   </si>
   <si>
     <t>Problem 8-18 Variable Growth (LG8-6)</t>
@@ -2481,7 +2478,7 @@
         <v>98</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2965,10 +2962,10 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" customWidth="1"/>
@@ -3296,10 +3293,7 @@
       <c r="B17" t="s">
         <v>222</v>
       </c>
-      <c r="C17" s="194">
-        <f>D3</f>
-        <v>875</v>
-      </c>
+      <c r="C17" s="194"/>
       <c r="D17" s="98"/>
       <c r="E17" s="98"/>
       <c r="F17" s="98"/>
@@ -3310,10 +3304,7 @@
       <c r="B18" t="s">
         <v>223</v>
       </c>
-      <c r="C18" s="98">
-        <f>D4</f>
-        <v>640</v>
-      </c>
+      <c r="C18" s="98"/>
       <c r="D18" s="98"/>
       <c r="E18" s="98"/>
       <c r="F18" s="98"/>
@@ -3336,10 +3327,7 @@
       <c r="B20" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="195">
-        <f>H3</f>
-        <v>0.21</v>
-      </c>
+      <c r="C20" s="195"/>
       <c r="D20" s="98"/>
       <c r="E20" s="98"/>
       <c r="F20" s="98"/>
@@ -3362,10 +3350,7 @@
       <c r="B22" t="s">
         <v>225</v>
       </c>
-      <c r="C22" s="195">
-        <f>H4</f>
-        <v>0.14249999999999999</v>
-      </c>
+      <c r="C22" s="195"/>
       <c r="D22" s="98"/>
       <c r="E22" s="98"/>
       <c r="F22" s="98"/>
@@ -3388,10 +3373,7 @@
       <c r="B25" t="s">
         <v>226</v>
       </c>
-      <c r="C25" s="196">
-        <f>J4</f>
-        <v>27.5625</v>
-      </c>
+      <c r="C25" s="196"/>
       <c r="D25" s="98"/>
       <c r="E25" s="98"/>
       <c r="F25" s="98"/>
@@ -3414,10 +3396,7 @@
       <c r="B27" t="s">
         <v>227</v>
       </c>
-      <c r="C27" s="196">
-        <f>J3</f>
-        <v>19.36</v>
-      </c>
+      <c r="C27" s="196"/>
       <c r="D27" s="98"/>
       <c r="E27" s="98"/>
       <c r="F27" s="98"/>
@@ -3451,33 +3430,18 @@
       <c r="B31" t="s">
         <v>228</v>
       </c>
-      <c r="C31" s="12">
-        <f>L3</f>
-        <v>14.87603305785124</v>
-      </c>
+      <c r="C31" s="12"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>229</v>
       </c>
-      <c r="C32" t="str">
-        <f>IF(M3&gt;0,"Over","Under")</f>
-        <v>Over</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>230</v>
       </c>
-      <c r="C33" s="12">
-        <f>M3</f>
-        <v>1.1239669421487601</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>231</v>
-      </c>
+      <c r="C33" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3501,7 +3465,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="99" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3509,7 +3473,7 @@
       <c r="B4" s="197"/>
       <c r="C4" s="197"/>
       <c r="D4" s="197" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E4" s="197"/>
       <c r="F4" s="197"/>
@@ -3519,13 +3483,13 @@
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="199" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B5" s="83">
         <v>0.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E5" s="119">
         <v>0</v>
@@ -3540,18 +3504,18 @@
         <v>3</v>
       </c>
       <c r="I5" s="200" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B6" s="87">
         <v>0.18</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E6" s="201"/>
       <c r="F6" s="177">
@@ -3570,13 +3534,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="86">
         <v>0.1</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E7" s="174"/>
       <c r="F7" s="176"/>
@@ -3594,7 +3558,7 @@
         <v>0.12</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E8" s="203">
         <f>NPV(B8,F6,G6,H6+I7)</f>
@@ -3607,7 +3571,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B9" s="100">
         <v>3</v>
@@ -3619,7 +3583,7 @@
       <c r="B10" s="197"/>
       <c r="C10" s="197"/>
       <c r="D10" s="197" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E10" s="204"/>
       <c r="F10" s="197"/>
@@ -3629,14 +3593,14 @@
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="199" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B11" s="12">
         <f>B5</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E11" s="119">
         <v>0</v>
@@ -3651,19 +3615,19 @@
         <v>3</v>
       </c>
       <c r="I11" s="205" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="199" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1">
         <f>B6</f>
         <v>0.18</v>
       </c>
       <c r="D12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E12" s="65"/>
       <c r="F12" s="12">
@@ -3682,14 +3646,14 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="199" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B13" s="206">
         <f>B7</f>
         <v>0.1</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E13" s="64"/>
       <c r="I13" s="207">
@@ -3728,7 +3692,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B15" s="211">
         <f>B9</f>
@@ -3736,7 +3700,7 @@
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E15" s="212">
         <f>SUM(F14:I14)</f>
@@ -3981,13 +3945,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" t="s">
         <v>280</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>281</v>
-      </c>
-      <c r="E5" t="s">
-        <v>282</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>200</v>
@@ -3995,7 +3959,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B6" s="12">
         <v>42.88</v>
@@ -4018,7 +3982,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B7" s="12">
         <v>51.32</v>
@@ -4041,7 +4005,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B8" s="12">
         <v>8.51</v>
@@ -4080,7 +4044,7 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2">
         <v>500</v>
@@ -4088,7 +4052,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C3" s="12">
         <v>103.39</v>
@@ -4096,7 +4060,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C4" s="127">
         <v>0.35</v>
@@ -4104,7 +4068,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5" s="12">
         <v>106.69</v>
@@ -4112,7 +4076,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="12">
         <f>((C5-C3)+C4)*C2</f>
@@ -4121,7 +4085,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" s="11">
         <f>C7/(C3*C2)</f>
@@ -4147,22 +4111,22 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B5" s="10">
         <v>30000</v>
@@ -4199,7 +4163,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="213" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S9" s="58"/>
     </row>
@@ -4223,13 +4187,13 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="213" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S13" s="58"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="S14" s="58"/>
     </row>
@@ -4274,7 +4238,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B18" s="2">
         <f>B16+B17</f>
@@ -4283,7 +4247,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B21" s="2">
         <v>0.15</v>
@@ -4291,7 +4255,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B22" s="1">
         <v>0.05</v>
@@ -4299,7 +4263,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="216" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B24" s="217">
         <f>(B21*B17)+(B22*B16)</f>
@@ -4308,7 +4272,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" s="10">
         <v>30000</v>
@@ -4316,12 +4280,12 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="216" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31" s="218">
         <f>B27/B24</f>
@@ -4347,7 +4311,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4355,7 +4319,7 @@
         <v>63</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4363,7 +4327,7 @@
         <v>65</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4378,7 +4342,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="213" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4389,7 +4353,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B10" s="12">
         <v>50</v>
@@ -4413,7 +4377,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B13" s="1">
         <v>0.05</v>
@@ -4421,7 +4385,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" s="1">
         <v>0.15</v>
@@ -4429,7 +4393,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B16" s="21">
         <f>B13+B12*(B14-B13)</f>
@@ -5704,7 +5668,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B25" s="12"/>
     </row>
@@ -5956,7 +5920,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5964,12 +5928,12 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" s="125">
         <v>5000</v>
@@ -5993,7 +5957,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B9" s="222">
         <f xml:space="preserve"> NPER(B7,0,B5,-B6)</f>
@@ -6002,7 +5966,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B11">
         <f>72/9</f>
@@ -6027,7 +5991,7 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B3" s="256">
         <v>2000</v>
@@ -6035,7 +5999,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B4" s="256">
         <v>150000</v>
@@ -6043,7 +6007,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -6059,7 +6023,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B7">
         <f>B5*B6</f>
@@ -6098,7 +6062,7 @@
   <sheetData>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="259" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B3" s="260"/>
       <c r="C3" s="260"/>
@@ -6115,7 +6079,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B7" s="257">
         <v>10000</v>
@@ -6131,7 +6095,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" s="258">
         <f>NPER(B8,0,B6,-B7)</f>
@@ -6296,7 +6260,7 @@
         <v>100</v>
       </c>
       <c r="I1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
@@ -6312,7 +6276,7 @@
         <v>14.5</v>
       </c>
       <c r="I2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -6338,7 +6302,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6367,7 +6331,7 @@
         <v>0.03</v>
       </c>
       <c r="I6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
